--- a/Timesheet_Reconciliation_HOURS_ONLY_Jonathan_Hendratno.xlsx
+++ b/Timesheet_Reconciliation_HOURS_ONLY_Jonathan_Hendratno.xlsx
@@ -1335,7 +1335,7 @@
     <row r="19">
       <c r="A19" s="36" t="inlineStr">
         <is>
-          <t>C.  DAY-BY-DAY RECONCILIATION  -  every timesheet line matched to the pay run that paid it</t>
+          <t>C.  DAY-BY-DAY RECONCILIATION  -  every timesheet line matched to the pay run that paid it.  The Notes column shows how each day was split across pay lines either side of the unpaid break.</t>
         </is>
       </c>
       <c r="B19" s="36" t="n"/>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="L22" s="44" t="inlineStr">
         <is>
-          <t>Two separate timesheets this day - matched by location</t>
+          <t>Paid as a single 4 hr line - no break taken. Two separate timesheets this day - matched by location</t>
         </is>
       </c>
       <c r="M22" s="24" t="n"/>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="L23" s="44" t="inlineStr">
         <is>
-          <t>Two separate timesheets this day - matched by location</t>
+          <t>Paid as a single 4 hr line - no break taken. Two separate timesheets this day - matched by location</t>
         </is>
       </c>
       <c r="M23" s="24" t="n"/>
@@ -1724,7 +1724,11 @@
         <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A25,'07 Aug 2026'!$K$3:$K$6,$D25)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A25,'21 Aug 2026'!$K$3:$K$7,$D25)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A25,'20 Sept 2026 '!$K$3:$K$14,$D25)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A25,'22 Sep 2026'!$K$3:$K$11,$D25)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
         <v/>
       </c>
-      <c r="L25" s="44" t="inlineStr"/>
+      <c r="L25" s="44" t="inlineStr">
+        <is>
+          <t>Paid as a single 4 hr line - no break taken</t>
+        </is>
+      </c>
       <c r="M25" s="24" t="n"/>
       <c r="N25" s="24" t="n"/>
       <c r="O25" s="24" t="n"/>
@@ -2391,7 +2395,11 @@
         <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A36,'07 Aug 2026'!$K$3:$K$6,$D36)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A36,'21 Aug 2026'!$K$3:$K$7,$D36)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A36,'20 Sept 2026 '!$K$3:$K$14,$D36)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A36,'22 Sep 2026'!$K$3:$K$11,$D36)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
         <v/>
       </c>
-      <c r="L36" s="44" t="inlineStr"/>
+      <c r="L36" s="44" t="inlineStr">
+        <is>
+          <t>Paid as a single 4 hr line - no break taken</t>
+        </is>
+      </c>
       <c r="M36" s="24" t="n"/>
       <c r="N36" s="24" t="n"/>
       <c r="O36" s="24" t="n"/>

--- a/Timesheet_Reconciliation_HOURS_ONLY_Jonathan_Hendratno.xlsx
+++ b/Timesheet_Reconciliation_HOURS_ONLY_Jonathan_Hendratno.xlsx
@@ -86,7 +86,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -147,6 +147,11 @@
         <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -175,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -213,6 +218,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="3" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -223,23 +231,36 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="9" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="3" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -674,21 +695,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T90"/>
+  <dimension ref="A1:V95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" style="17" min="1" max="1"/>
-    <col width="11" bestFit="1" customWidth="1" style="17" min="2" max="2"/>
-    <col width="34" customWidth="1" style="17" min="3" max="4"/>
-    <col width="34" customWidth="1" style="12" min="4" max="4"/>
-    <col width="10" bestFit="1" customWidth="1" style="17" min="5" max="5"/>
+    <col width="30" customWidth="1" style="17" min="1" max="1"/>
+    <col width="9" bestFit="1" customWidth="1" style="17" min="2" max="2"/>
+    <col width="26" customWidth="1" style="17" min="3" max="4"/>
+    <col width="12" customWidth="1" style="12" min="4" max="4"/>
+    <col width="34" bestFit="1" customWidth="1" style="17" min="5" max="5"/>
     <col width="10" customWidth="1" style="17" min="6" max="16384"/>
-    <col width="12" customWidth="1" style="12" min="7" max="7"/>
-    <col width="11" customWidth="1" style="12" min="8" max="8"/>
-    <col width="12" customWidth="1" style="12" min="9" max="9"/>
-    <col width="10" customWidth="1" style="12" min="10" max="10"/>
-    <col width="14" customWidth="1" style="12" min="11" max="11"/>
-    <col width="46" customWidth="1" style="12" min="12" max="12"/>
+    <col width="10" customWidth="1" style="12" min="7" max="7"/>
+    <col width="12" customWidth="1" style="12" min="8" max="8"/>
+    <col width="11" customWidth="1" style="12" min="9" max="9"/>
+    <col width="11" customWidth="1" style="12" min="10" max="10"/>
+    <col width="11" customWidth="1" style="12" min="11" max="11"/>
+    <col width="52" customWidth="1" style="12" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="4.5" customHeight="1" s="12">
@@ -716,11 +737,13 @@
       <c r="R1" s="24" t="n"/>
       <c r="S1" s="24" t="n"/>
       <c r="T1" s="24" t="n"/>
-    </row>
-    <row r="2" ht="28" customHeight="1" s="12">
+      <c r="U1" s="24" t="n"/>
+      <c r="V1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="12">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Hours only - no rates, gross pay or superannuation appear anywhere in this file. Timesheet hours transcribed from the timesheet screenshots (fortnights ending 07/08/2026, 21/08/2026, 04/09/2026 and 18/09/2026). Paid hours are pulled live by formula from the pay-run tabs in this workbook, matched on work date AND location. Prepared 22/09/2026.</t>
+          <t>Hours only - no rates, gross pay or superannuation appear anywhere in this file. Timesheet hours transcribed from the timesheet screenshots. Paid hours are pulled live by formula from the pay-run tabs, matched on work date AND location. Pay periods and dates paid are taken from the Employment Hero pay history. Prepared 22/09/2026.</t>
         </is>
       </c>
       <c r="M2" s="24" t="n"/>
@@ -731,6 +754,8 @@
       <c r="R2" s="24" t="n"/>
       <c r="S2" s="24" t="n"/>
       <c r="T2" s="24" t="n"/>
+      <c r="U2" s="24" t="n"/>
+      <c r="V2" s="24" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="24" t="n"/>
@@ -753,6 +778,8 @@
       <c r="R3" s="24" t="n"/>
       <c r="S3" s="24" t="n"/>
       <c r="T3" s="24" t="n"/>
+      <c r="U3" s="24" t="n"/>
+      <c r="V3" s="24" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
@@ -779,8 +806,10 @@
       <c r="R4" s="24" t="n"/>
       <c r="S4" s="24" t="n"/>
       <c r="T4" s="24" t="n"/>
-    </row>
-    <row r="5" ht="30" customHeight="1" s="12">
+      <c r="U4" s="24" t="n"/>
+      <c r="V4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="32" customHeight="1" s="12">
       <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Date</t>
@@ -797,40 +826,44 @@
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>Pay Period</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>Date
+Paid</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Hours
 Claimed Missing</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>Hours
 Actually Paid</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Shortfall
 (Hrs)</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
-        <is>
-          <t>Paid in
-Pay Run</t>
-        </is>
-      </c>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Where to find it on that tab</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="J5" s="27" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="J5" s="24" t="n"/>
       <c r="K5" s="24" t="n"/>
       <c r="L5" s="24" t="n"/>
       <c r="M5" s="24" t="n"/>
@@ -841,6 +874,8 @@
       <c r="R5" s="24" t="n"/>
       <c r="S5" s="24" t="n"/>
       <c r="T5" s="24" t="n"/>
+      <c r="U5" s="24" t="n"/>
+      <c r="V5" s="24" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="28" t="n">
@@ -856,31 +891,34 @@
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="D6" s="31" t="n">
+      <c r="D6" s="30" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>46273</v>
+      </c>
+      <c r="F6" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="E6" s="31">
+      <c r="G6" s="32">
         <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A6,'07 Aug 2026'!$K$3:$K$6,$C6)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A6,'21 Aug 2026'!$K$3:$K$7,$C6)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A6,'20 Sept 2026 '!$K$3:$K$14,$C6)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A6,'22 Sep 2026'!$K$3:$K$11,$C6)</f>
         <v/>
       </c>
-      <c r="F6" s="31">
-        <f>D6-E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="29">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A6,'07 Aug 2026'!$K$3:$K$6,$C6)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A6,'21 Aug 2026'!$K$3:$K$7,$C6)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A6,'20 Sept 2026 '!$K$3:$K$14,$C6)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A6,'22 Sep 2026'!$K$3:$K$11,$C6)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="H6" s="32" t="inlineStr">
+      <c r="H6" s="32">
+        <f>F6-G6</f>
+        <v/>
+      </c>
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t>'20 Sept 2026 ' rows 3 and 4  (3.5 hrs 08:30-12:00  +  4.5 hrs 12:30-17:00)</t>
         </is>
       </c>
-      <c r="I6" s="29">
-        <f>IF(ROUND(F6,2)=0,"PAID IN FULL - nothing owing","SHORTFALL - investigate")</f>
-        <v/>
-      </c>
-      <c r="J6" s="24" t="n"/>
+      <c r="J6" s="29">
+        <f>IF(ROUND(H6,2)=0,"PAID IN FULL - nothing owing","SHORTFALL - investigate")</f>
+        <v/>
+      </c>
       <c r="K6" s="24" t="n"/>
       <c r="L6" s="24" t="n"/>
       <c r="M6" s="24" t="n"/>
@@ -891,6 +929,8 @@
       <c r="R6" s="24" t="n"/>
       <c r="S6" s="24" t="n"/>
       <c r="T6" s="24" t="n"/>
+      <c r="U6" s="24" t="n"/>
+      <c r="V6" s="24" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="28" t="n">
@@ -906,31 +946,34 @@
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="D7" s="31" t="n">
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>46273</v>
+      </c>
+      <c r="F7" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="E7" s="31">
+      <c r="G7" s="32">
         <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A7,'07 Aug 2026'!$K$3:$K$6,$C7)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A7,'21 Aug 2026'!$K$3:$K$7,$C7)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A7,'20 Sept 2026 '!$K$3:$K$14,$C7)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A7,'22 Sep 2026'!$K$3:$K$11,$C7)</f>
         <v/>
       </c>
-      <c r="F7" s="31">
-        <f>D7-E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="29">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A7,'07 Aug 2026'!$K$3:$K$6,$C7)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A7,'21 Aug 2026'!$K$3:$K$7,$C7)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A7,'20 Sept 2026 '!$K$3:$K$14,$C7)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A7,'22 Sep 2026'!$K$3:$K$11,$C7)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="H7" s="32" t="inlineStr">
+      <c r="H7" s="32">
+        <f>F7-G7</f>
+        <v/>
+      </c>
+      <c r="I7" s="33" t="inlineStr">
         <is>
           <t>'20 Sept 2026 ' rows 5 and 6  (3.5 hrs 08:30-12:00  +  4.5 hrs 12:30-17:00)</t>
         </is>
       </c>
-      <c r="I7" s="29">
-        <f>IF(ROUND(F7,2)=0,"PAID IN FULL - nothing owing","SHORTFALL - investigate")</f>
-        <v/>
-      </c>
-      <c r="J7" s="24" t="n"/>
+      <c r="J7" s="29">
+        <f>IF(ROUND(H7,2)=0,"PAID IN FULL - nothing owing","SHORTFALL - investigate")</f>
+        <v/>
+      </c>
       <c r="K7" s="24" t="n"/>
       <c r="L7" s="24" t="n"/>
       <c r="M7" s="24" t="n"/>
@@ -941,34 +984,36 @@
       <c r="R7" s="24" t="n"/>
       <c r="S7" s="24" t="n"/>
       <c r="T7" s="24" t="n"/>
+      <c r="U7" s="24" t="n"/>
+      <c r="V7" s="24" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>TOTAL CLAIMED</t>
         </is>
       </c>
-      <c r="B8" s="33" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="34">
-        <f>SUM(D6:D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="34">
-        <f>SUM(E6:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="34">
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="34" t="n"/>
+      <c r="F8" s="35">
         <f>SUM(F6:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="33" t="n"/>
-      <c r="H8" s="33" t="n"/>
-      <c r="I8" s="33">
-        <f>IF(ROUND(F8,2)=0,"NIL OWING - all "&amp;TEXT(D8,"0")&amp;" hrs paid","HOURS OWING - investigate")</f>
-        <v/>
-      </c>
-      <c r="J8" s="24" t="n"/>
+      <c r="G8" s="35">
+        <f>SUM(G6:G7)</f>
+        <v/>
+      </c>
+      <c r="H8" s="35">
+        <f>SUM(H6:H7)</f>
+        <v/>
+      </c>
+      <c r="I8" s="34" t="n"/>
+      <c r="J8" s="34">
+        <f>IF(ROUND(H8,2)=0,"NIL OWING - all "&amp;TEXT(F8,"0")&amp;" hrs paid","HOURS OWING - investigate")</f>
+        <v/>
+      </c>
       <c r="K8" s="24" t="n"/>
       <c r="L8" s="24" t="n"/>
       <c r="M8" s="24" t="n"/>
@@ -979,11 +1024,13 @@
       <c r="R8" s="24" t="n"/>
       <c r="S8" s="24" t="n"/>
       <c r="T8" s="24" t="n"/>
-    </row>
-    <row r="9" ht="46" customHeight="1" s="12">
-      <c r="A9" s="35" t="inlineStr">
-        <is>
-          <t>WHY IT LOOKED MISSING:  (1) Each day is split across two pay lines, either side of the lunch break - 3.5 hrs + 4.5 hrs - so neither line ever shows as "8 hours" when you scan the payslip.  (2) Both days sit in the fortnight ending 04/09/2026, but that fortnight was paid across TWO pay runs: the 48 hrs of DTTL work went through the 20 Sep 2026 run, while the 23.5 hrs of PwC work went through the 22 Sep 2026 run. Looking at only one of those payslips shows only part of the fortnight.</t>
+      <c r="U8" s="24" t="n"/>
+      <c r="V8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="32" customHeight="1" s="12">
+      <c r="A9" s="36" t="inlineStr">
+        <is>
+          <t>WHY IT LOOKED MISSING:  Each day is split across two pay lines, either side of the unpaid lunch break - 3.5 hrs + 4.5 hrs - so neither line ever shows as "8 hours" when you scan the payslip. Both days fall in the pay period 22/08/2026 - 04/09/2026, paid on 08/09/2026.</t>
         </is>
       </c>
       <c r="M9" s="24" t="n"/>
@@ -994,6 +1041,8 @@
       <c r="R9" s="24" t="n"/>
       <c r="S9" s="24" t="n"/>
       <c r="T9" s="24" t="n"/>
+      <c r="U9" s="24" t="n"/>
+      <c r="V9" s="24" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="24" t="n"/>
@@ -1016,24 +1065,26 @@
       <c r="R10" s="24" t="n"/>
       <c r="S10" s="24" t="n"/>
       <c r="T10" s="24" t="n"/>
+      <c r="U10" s="24" t="n"/>
+      <c r="V10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
-        <is>
-          <t>B.  FORTNIGHT SUMMARY  -  timesheet hours vs hours actually paid</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
-      <c r="G11" s="36" t="n"/>
-      <c r="H11" s="36" t="n"/>
-      <c r="I11" s="36" t="n"/>
-      <c r="J11" s="36" t="n"/>
-      <c r="K11" s="36" t="n"/>
-      <c r="L11" s="36" t="n"/>
+      <c r="A11" s="37" t="inlineStr">
+        <is>
+          <t>B.  PAY PERIOD SUMMARY  -  timesheet hours vs hours paid, by pay period and the date each was paid</t>
+        </is>
+      </c>
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="37" t="n"/>
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="37" t="n"/>
+      <c r="F11" s="37" t="n"/>
+      <c r="G11" s="37" t="n"/>
+      <c r="H11" s="37" t="n"/>
+      <c r="I11" s="37" t="n"/>
+      <c r="J11" s="37" t="n"/>
+      <c r="K11" s="37" t="n"/>
+      <c r="L11" s="37" t="n"/>
       <c r="M11" s="24" t="n"/>
       <c r="N11" s="24" t="n"/>
       <c r="O11" s="24" t="n"/>
@@ -1042,48 +1093,55 @@
       <c r="R11" s="24" t="n"/>
       <c r="S11" s="24" t="n"/>
       <c r="T11" s="24" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1" s="12">
+      <c r="U11" s="24" t="n"/>
+      <c r="V11" s="24" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1" s="12">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>Fortnight Ending</t>
+          <t>Pay Period</t>
         </is>
       </c>
       <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>Date
+Paid</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Source Tab in Workbook</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Timesheets
 (count)</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>Timesheet
 Hours</t>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="F12" s="27" t="inlineStr">
         <is>
           <t>Paid
 Hours</t>
         </is>
       </c>
-      <c r="E12" s="27" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>Variance
 (Hrs)</t>
         </is>
       </c>
-      <c r="F12" s="27" t="inlineStr">
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G12" s="27" t="inlineStr">
-        <is>
-          <t>Paid in Pay Run(s)</t>
-        </is>
-      </c>
-      <c r="H12" s="24" t="n"/>
       <c r="I12" s="24" t="n"/>
       <c r="J12" s="24" t="n"/>
       <c r="K12" s="24" t="n"/>
@@ -1096,37 +1154,43 @@
       <c r="R12" s="24" t="n"/>
       <c r="S12" s="24" t="n"/>
       <c r="T12" s="24" t="n"/>
+      <c r="U12" s="24" t="n"/>
+      <c r="V12" s="24" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="n">
-        <v>46241</v>
-      </c>
-      <c r="B13" s="38">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>25/07/2026 - 07/08/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="39" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C13" s="38" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="40">
         <f>COUNTIFS($C$21:$C$36,$A13)</f>
         <v/>
       </c>
-      <c r="C13" s="39">
-        <f>SUMIFS($H$21:$H$36,$C$21:$C$36,$A13)</f>
-        <v/>
-      </c>
-      <c r="D13" s="39">
+      <c r="E13" s="41">
         <f>SUMIFS($I$21:$I$36,$C$21:$C$36,$A13)</f>
         <v/>
       </c>
-      <c r="E13" s="39">
-        <f>C13-D13</f>
-        <v/>
-      </c>
-      <c r="F13" s="40">
-        <f>IF(ROUND(E13,2)=0,"Reconciled","VARIANCE - investigate")</f>
-        <v/>
-      </c>
-      <c r="G13" s="40" t="inlineStr">
-        <is>
-          <t>07 Aug 2026</t>
-        </is>
-      </c>
-      <c r="H13" s="24" t="n"/>
+      <c r="F13" s="41">
+        <f>SUMIFS($J$21:$J$36,$C$21:$C$36,$A13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="41">
+        <f>E13-F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="38">
+        <f>IF(ROUND(G13,2)=0,"Reconciled","VARIANCE - investigate")</f>
+        <v/>
+      </c>
       <c r="I13" s="24" t="n"/>
       <c r="J13" s="24" t="n"/>
       <c r="K13" s="24" t="n"/>
@@ -1139,37 +1203,43 @@
       <c r="R13" s="24" t="n"/>
       <c r="S13" s="24" t="n"/>
       <c r="T13" s="24" t="n"/>
+      <c r="U13" s="24" t="n"/>
+      <c r="V13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="n">
-        <v>46255</v>
-      </c>
-      <c r="B14" s="38">
+      <c r="A14" s="38" t="inlineStr">
+        <is>
+          <t>08/08/2026 - 21/08/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
+        <is>
+          <t>21 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="40">
         <f>COUNTIFS($C$21:$C$36,$A14)</f>
         <v/>
       </c>
-      <c r="C14" s="39">
-        <f>SUMIFS($H$21:$H$36,$C$21:$C$36,$A14)</f>
-        <v/>
-      </c>
-      <c r="D14" s="39">
+      <c r="E14" s="41">
         <f>SUMIFS($I$21:$I$36,$C$21:$C$36,$A14)</f>
         <v/>
       </c>
-      <c r="E14" s="39">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="40">
-        <f>IF(ROUND(E14,2)=0,"Reconciled","VARIANCE - investigate")</f>
-        <v/>
-      </c>
-      <c r="G14" s="40" t="inlineStr">
-        <is>
-          <t>21 Aug 2026</t>
-        </is>
-      </c>
-      <c r="H14" s="24" t="n"/>
+      <c r="F14" s="41">
+        <f>SUMIFS($J$21:$J$36,$C$21:$C$36,$A14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="41">
+        <f>E14-F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="38">
+        <f>IF(ROUND(G14,2)=0,"Reconciled","VARIANCE - investigate")</f>
+        <v/>
+      </c>
       <c r="I14" s="24" t="n"/>
       <c r="J14" s="24" t="n"/>
       <c r="K14" s="24" t="n"/>
@@ -1182,37 +1252,43 @@
       <c r="R14" s="24" t="n"/>
       <c r="S14" s="24" t="n"/>
       <c r="T14" s="24" t="n"/>
+      <c r="U14" s="24" t="n"/>
+      <c r="V14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B15" s="38">
+      <c r="A15" s="38" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="39" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>20 Sept 2026 + 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D15" s="40">
         <f>COUNTIFS($C$21:$C$36,$A15)</f>
         <v/>
       </c>
-      <c r="C15" s="39">
-        <f>SUMIFS($H$21:$H$36,$C$21:$C$36,$A15)</f>
-        <v/>
-      </c>
-      <c r="D15" s="39">
+      <c r="E15" s="41">
         <f>SUMIFS($I$21:$I$36,$C$21:$C$36,$A15)</f>
         <v/>
       </c>
-      <c r="E15" s="39">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="40">
-        <f>IF(ROUND(E15,2)=0,"Reconciled","VARIANCE - investigate")</f>
-        <v/>
-      </c>
-      <c r="G15" s="40" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 (DTTL 48 hrs) + 22 Sep 2026 (PwC 23.5 hrs)</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="n"/>
+      <c r="F15" s="41">
+        <f>SUMIFS($J$21:$J$36,$C$21:$C$36,$A15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="41">
+        <f>E15-F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="38">
+        <f>IF(ROUND(G15,2)=0,"Reconciled","VARIANCE - investigate")</f>
+        <v/>
+      </c>
       <c r="I15" s="24" t="n"/>
       <c r="J15" s="24" t="n"/>
       <c r="K15" s="24" t="n"/>
@@ -1225,37 +1301,43 @@
       <c r="R15" s="24" t="n"/>
       <c r="S15" s="24" t="n"/>
       <c r="T15" s="24" t="n"/>
+      <c r="U15" s="24" t="n"/>
+      <c r="V15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B16" s="38">
+      <c r="A16" s="38" t="inlineStr">
+        <is>
+          <t>05/09/2026 - 18/09/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="39" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="40">
         <f>COUNTIFS($C$21:$C$36,$A16)</f>
         <v/>
       </c>
-      <c r="C16" s="39">
-        <f>SUMIFS($H$21:$H$36,$C$21:$C$36,$A16)</f>
-        <v/>
-      </c>
-      <c r="D16" s="39">
+      <c r="E16" s="41">
         <f>SUMIFS($I$21:$I$36,$C$21:$C$36,$A16)</f>
         <v/>
       </c>
-      <c r="E16" s="39">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="40">
-        <f>IF(ROUND(E16,2)=0,"Reconciled","VARIANCE - investigate")</f>
-        <v/>
-      </c>
-      <c r="G16" s="40" t="inlineStr">
-        <is>
-          <t>22 Sep 2026</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="n"/>
+      <c r="F16" s="41">
+        <f>SUMIFS($J$21:$J$36,$C$21:$C$36,$A16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="41">
+        <f>E16-F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="38">
+        <f>IF(ROUND(G16,2)=0,"Reconciled","VARIANCE - investigate")</f>
+        <v/>
+      </c>
       <c r="I16" s="24" t="n"/>
       <c r="J16" s="24" t="n"/>
       <c r="K16" s="24" t="n"/>
@@ -1268,22 +1350,18 @@
       <c r="R16" s="24" t="n"/>
       <c r="S16" s="24" t="n"/>
       <c r="T16" s="24" t="n"/>
+      <c r="U16" s="24" t="n"/>
+      <c r="V16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="41" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="42">
-        <f>SUM(B13:B16)</f>
-        <v/>
-      </c>
-      <c r="C17" s="43">
-        <f>SUM(C13:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="43">
+      <c r="B17" s="42" t="n"/>
+      <c r="C17" s="42" t="n"/>
+      <c r="D17" s="42">
         <f>SUM(D13:D16)</f>
         <v/>
       </c>
@@ -1291,12 +1369,18 @@
         <f>SUM(E13:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="41">
-        <f>IF(ROUND(E17,2)=0,"FULLY RECONCILED","VARIANCE - investigate")</f>
-        <v/>
-      </c>
-      <c r="G17" s="41" t="n"/>
-      <c r="H17" s="24" t="n"/>
+      <c r="F17" s="43">
+        <f>SUM(F13:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="43">
+        <f>SUM(G13:G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="42">
+        <f>IF(ROUND(G17,2)=0,"FULLY RECONCILED","VARIANCE - investigate")</f>
+        <v/>
+      </c>
       <c r="I17" s="24" t="n"/>
       <c r="J17" s="24" t="n"/>
       <c r="K17" s="24" t="n"/>
@@ -1309,6 +1393,8 @@
       <c r="R17" s="24" t="n"/>
       <c r="S17" s="24" t="n"/>
       <c r="T17" s="24" t="n"/>
+      <c r="U17" s="24" t="n"/>
+      <c r="V17" s="24" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="24" t="n"/>
@@ -1331,24 +1417,26 @@
       <c r="R18" s="24" t="n"/>
       <c r="S18" s="24" t="n"/>
       <c r="T18" s="24" t="n"/>
+      <c r="U18" s="24" t="n"/>
+      <c r="V18" s="24" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
-        <is>
-          <t>C.  DAY-BY-DAY RECONCILIATION  -  every timesheet line matched to the pay run that paid it.  The Notes column shows how each day was split across pay lines either side of the unpaid break.</t>
-        </is>
-      </c>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
-      <c r="H19" s="36" t="n"/>
-      <c r="I19" s="36" t="n"/>
-      <c r="J19" s="36" t="n"/>
-      <c r="K19" s="36" t="n"/>
-      <c r="L19" s="36" t="n"/>
+      <c r="A19" s="37" t="inlineStr">
+        <is>
+          <t>C.  DAY-BY-DAY RECONCILIATION  -  every timesheet line matched to the pay period that paid it.  The Notes column shows how each day was split across pay lines either side of the unpaid break.</t>
+        </is>
+      </c>
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="37" t="n"/>
+      <c r="G19" s="37" t="n"/>
+      <c r="H19" s="37" t="n"/>
+      <c r="I19" s="37" t="n"/>
+      <c r="J19" s="37" t="n"/>
+      <c r="K19" s="37" t="n"/>
+      <c r="L19" s="37" t="n"/>
       <c r="M19" s="24" t="n"/>
       <c r="N19" s="24" t="n"/>
       <c r="O19" s="24" t="n"/>
@@ -1357,8 +1445,10 @@
       <c r="R19" s="24" t="n"/>
       <c r="S19" s="24" t="n"/>
       <c r="T19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="30" customHeight="1" s="12">
+      <c r="U19" s="24" t="n"/>
+      <c r="V19" s="24" t="n"/>
+    </row>
+    <row r="20" ht="32" customHeight="1" s="12">
       <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Date</t>
@@ -1371,52 +1461,51 @@
       </c>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>Fortnight
-Ending</t>
+          <t>Pay Period</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
         <is>
+          <t>Date
+Paid</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
           <t>Location / Client (per timesheet)</t>
         </is>
       </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="F20" s="27" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="F20" s="27" t="inlineStr">
+      <c r="G20" s="27" t="inlineStr">
         <is>
           <t>End</t>
         </is>
       </c>
-      <c r="G20" s="27" t="inlineStr">
+      <c r="H20" s="27" t="inlineStr">
         <is>
           <t>Break</t>
         </is>
       </c>
-      <c r="H20" s="27" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Timesheet
 Hours</t>
         </is>
       </c>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="J20" s="27" t="inlineStr">
         <is>
           <t>Paid
 Hours</t>
         </is>
       </c>
-      <c r="J20" s="27" t="inlineStr">
+      <c r="K20" s="27" t="inlineStr">
         <is>
           <t>Variance
 (Hrs)</t>
-        </is>
-      </c>
-      <c r="K20" s="27" t="inlineStr">
-        <is>
-          <t>Paid in
-Pay Run</t>
         </is>
       </c>
       <c r="L20" s="27" t="inlineStr">
@@ -1432,57 +1521,60 @@
       <c r="R20" s="24" t="n"/>
       <c r="S20" s="24" t="n"/>
       <c r="T20" s="24" t="n"/>
+      <c r="U20" s="24" t="n"/>
+      <c r="V20" s="24" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="n">
+      <c r="A21" s="39" t="n">
         <v>46232</v>
       </c>
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C21" s="37" t="n">
-        <v>46241</v>
-      </c>
-      <c r="D21" s="40" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
+        <is>
+          <t>25/07/2026 - 07/08/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="44" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E21" s="38" t="inlineStr">
         <is>
           <t>CBA FT Tech MEL - 12 months [ONS]</t>
         </is>
       </c>
-      <c r="E21" s="38" t="inlineStr">
+      <c r="F21" s="40" t="inlineStr">
         <is>
           <t>7:00 AM</t>
         </is>
       </c>
-      <c r="F21" s="38" t="inlineStr">
+      <c r="G21" s="40" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="G21" s="38" t="inlineStr">
+      <c r="H21" s="40" t="inlineStr">
         <is>
           <t>12:30-1:30</t>
         </is>
       </c>
-      <c r="H21" s="39" t="n">
+      <c r="I21" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="I21" s="39">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A21,'07 Aug 2026'!$K$3:$K$6,$D21)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A21,'21 Aug 2026'!$K$3:$K$7,$D21)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A21,'20 Sept 2026 '!$K$3:$K$14,$D21)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A21,'22 Sep 2026'!$K$3:$K$11,$D21)</f>
-        <v/>
-      </c>
-      <c r="J21" s="39">
-        <f>H21-I21</f>
-        <v/>
-      </c>
-      <c r="K21" s="38">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A21,'07 Aug 2026'!$K$3:$K$6,$D21)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A21,'21 Aug 2026'!$K$3:$K$7,$D21)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A21,'20 Sept 2026 '!$K$3:$K$14,$D21)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A21,'22 Sep 2026'!$K$3:$K$11,$D21)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L21" s="44" t="inlineStr">
-        <is>
-          <t>Paid as 5.5 + 2.5 hrs either side of break</t>
+      <c r="J21" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A21,'07 Aug 2026'!$K$3:$K$6,$E21)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A21,'21 Aug 2026'!$K$3:$K$7,$E21)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A21,'20 Sept 2026 '!$K$3:$K$14,$E21)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A21,'22 Sep 2026'!$K$3:$K$11,$E21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="41">
+        <f>I21-J21</f>
+        <v/>
+      </c>
+      <c r="L21" s="45" t="inlineStr">
+        <is>
+          <t>Paid as 5.5 + 2.5 hrs either side of break. Rate later corrected to $37.50/hr - see Section D.</t>
         </is>
       </c>
       <c r="M21" s="24" t="n"/>
@@ -1493,57 +1585,60 @@
       <c r="R21" s="24" t="n"/>
       <c r="S21" s="24" t="n"/>
       <c r="T21" s="24" t="n"/>
+      <c r="U21" s="24" t="n"/>
+      <c r="V21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="37" t="n">
+      <c r="A22" s="39" t="n">
         <v>46233</v>
       </c>
-      <c r="B22" s="38" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C22" s="37" t="n">
-        <v>46241</v>
-      </c>
-      <c r="D22" s="40" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
+        <is>
+          <t>25/07/2026 - 07/08/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="44" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E22" s="38" t="inlineStr">
         <is>
           <t>PWC – MEL Technician [ONS]</t>
         </is>
       </c>
-      <c r="E22" s="38" t="inlineStr">
+      <c r="F22" s="40" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="F22" s="38" t="inlineStr">
+      <c r="G22" s="40" t="inlineStr">
         <is>
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="G22" s="38" t="inlineStr">
+      <c r="H22" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H22" s="39" t="n">
+      <c r="I22" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="I22" s="39">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A22,'07 Aug 2026'!$K$3:$K$6,$D22)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A22,'21 Aug 2026'!$K$3:$K$7,$D22)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A22,'20 Sept 2026 '!$K$3:$K$14,$D22)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A22,'22 Sep 2026'!$K$3:$K$11,$D22)</f>
-        <v/>
-      </c>
-      <c r="J22" s="39">
-        <f>H22-I22</f>
-        <v/>
-      </c>
-      <c r="K22" s="38">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A22,'07 Aug 2026'!$K$3:$K$6,$D22)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A22,'21 Aug 2026'!$K$3:$K$7,$D22)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A22,'20 Sept 2026 '!$K$3:$K$14,$D22)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A22,'22 Sep 2026'!$K$3:$K$11,$D22)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L22" s="44" t="inlineStr">
-        <is>
-          <t>Paid as a single 4 hr line - no break taken. Two separate timesheets this day - matched by location</t>
+      <c r="J22" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A22,'07 Aug 2026'!$K$3:$K$6,$E22)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A22,'21 Aug 2026'!$K$3:$K$7,$E22)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A22,'20 Sept 2026 '!$K$3:$K$14,$E22)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A22,'22 Sep 2026'!$K$3:$K$11,$E22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="41">
+        <f>I22-J22</f>
+        <v/>
+      </c>
+      <c r="L22" s="45" t="inlineStr">
+        <is>
+          <t>Paid as a single 4 hr line - no break taken. Two separate timesheets this day - matched by location. Rate later corrected to $37.50/hr - see Section D.</t>
         </is>
       </c>
       <c r="M22" s="24" t="n"/>
@@ -1554,57 +1649,60 @@
       <c r="R22" s="24" t="n"/>
       <c r="S22" s="24" t="n"/>
       <c r="T22" s="24" t="n"/>
+      <c r="U22" s="24" t="n"/>
+      <c r="V22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="n">
+      <c r="A23" s="39" t="n">
         <v>46233</v>
       </c>
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C23" s="37" t="n">
-        <v>46241</v>
-      </c>
-      <c r="D23" s="40" t="inlineStr">
+      <c r="C23" s="38" t="inlineStr">
+        <is>
+          <t>25/07/2026 - 07/08/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="44" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E23" s="38" t="inlineStr">
         <is>
           <t>Aware Super AV Maintenance [ONS]</t>
         </is>
       </c>
-      <c r="E23" s="38" t="inlineStr">
+      <c r="F23" s="40" t="inlineStr">
         <is>
           <t>2:25 PM</t>
         </is>
       </c>
-      <c r="F23" s="38" t="inlineStr">
+      <c r="G23" s="40" t="inlineStr">
         <is>
           <t>6:25 PM</t>
         </is>
       </c>
-      <c r="G23" s="38" t="inlineStr">
+      <c r="H23" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H23" s="39" t="n">
+      <c r="I23" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="I23" s="39">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A23,'07 Aug 2026'!$K$3:$K$6,$D23)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A23,'21 Aug 2026'!$K$3:$K$7,$D23)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A23,'20 Sept 2026 '!$K$3:$K$14,$D23)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A23,'22 Sep 2026'!$K$3:$K$11,$D23)</f>
-        <v/>
-      </c>
-      <c r="J23" s="39">
-        <f>H23-I23</f>
-        <v/>
-      </c>
-      <c r="K23" s="38">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A23,'07 Aug 2026'!$K$3:$K$6,$D23)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A23,'21 Aug 2026'!$K$3:$K$7,$D23)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A23,'20 Sept 2026 '!$K$3:$K$14,$D23)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A23,'22 Sep 2026'!$K$3:$K$11,$D23)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L23" s="44" t="inlineStr">
-        <is>
-          <t>Paid as a single 4 hr line - no break taken. Two separate timesheets this day - matched by location</t>
+      <c r="J23" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A23,'07 Aug 2026'!$K$3:$K$6,$E23)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A23,'21 Aug 2026'!$K$3:$K$7,$E23)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A23,'20 Sept 2026 '!$K$3:$K$14,$E23)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A23,'22 Sep 2026'!$K$3:$K$11,$E23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="41">
+        <f>I23-J23</f>
+        <v/>
+      </c>
+      <c r="L23" s="45" t="inlineStr">
+        <is>
+          <t>Paid as a single 4 hr line - no break taken. Two separate timesheets this day - matched by location. Rate later corrected to $37.50/hr - see Section D.</t>
         </is>
       </c>
       <c r="M23" s="24" t="n"/>
@@ -1615,55 +1713,58 @@
       <c r="R23" s="24" t="n"/>
       <c r="S23" s="24" t="n"/>
       <c r="T23" s="24" t="n"/>
+      <c r="U23" s="24" t="n"/>
+      <c r="V23" s="24" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="37" t="n">
+      <c r="A24" s="39" t="n">
         <v>46252</v>
       </c>
-      <c r="B24" s="38" t="inlineStr">
+      <c r="B24" s="40" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C24" s="37" t="n">
-        <v>46255</v>
-      </c>
-      <c r="D24" s="40" t="inlineStr">
+      <c r="C24" s="38" t="inlineStr">
+        <is>
+          <t>08/08/2026 - 21/08/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="44" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E24" s="38" t="inlineStr">
         <is>
           <t>CBA FT Tech MEL - 12 months [ONS]</t>
         </is>
       </c>
-      <c r="E24" s="38" t="inlineStr">
+      <c r="F24" s="40" t="inlineStr">
         <is>
           <t>7:00 AM</t>
         </is>
       </c>
-      <c r="F24" s="38" t="inlineStr">
+      <c r="G24" s="40" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="G24" s="38" t="inlineStr">
+      <c r="H24" s="40" t="inlineStr">
         <is>
           <t>12:00-1:00</t>
         </is>
       </c>
-      <c r="H24" s="39" t="n">
+      <c r="I24" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="I24" s="39">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A24,'07 Aug 2026'!$K$3:$K$6,$D24)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A24,'21 Aug 2026'!$K$3:$K$7,$D24)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A24,'20 Sept 2026 '!$K$3:$K$14,$D24)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A24,'22 Sep 2026'!$K$3:$K$11,$D24)</f>
-        <v/>
-      </c>
-      <c r="J24" s="39">
-        <f>H24-I24</f>
-        <v/>
-      </c>
-      <c r="K24" s="38">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A24,'07 Aug 2026'!$K$3:$K$6,$D24)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A24,'21 Aug 2026'!$K$3:$K$7,$D24)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A24,'20 Sept 2026 '!$K$3:$K$14,$D24)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A24,'22 Sep 2026'!$K$3:$K$11,$D24)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L24" s="44" t="inlineStr">
+      <c r="J24" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A24,'07 Aug 2026'!$K$3:$K$6,$E24)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A24,'21 Aug 2026'!$K$3:$K$7,$E24)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A24,'20 Sept 2026 '!$K$3:$K$14,$E24)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A24,'22 Sep 2026'!$K$3:$K$11,$E24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="41">
+        <f>I24-J24</f>
+        <v/>
+      </c>
+      <c r="L24" s="45" t="inlineStr">
         <is>
           <t>Paid as 5 + 3 hrs either side of break</t>
         </is>
@@ -1676,55 +1777,58 @@
       <c r="R24" s="24" t="n"/>
       <c r="S24" s="24" t="n"/>
       <c r="T24" s="24" t="n"/>
+      <c r="U24" s="24" t="n"/>
+      <c r="V24" s="24" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="n">
+      <c r="A25" s="39" t="n">
         <v>46254</v>
       </c>
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C25" s="37" t="n">
-        <v>46255</v>
-      </c>
-      <c r="D25" s="40" t="inlineStr">
+      <c r="C25" s="38" t="inlineStr">
+        <is>
+          <t>08/08/2026 - 21/08/2026</t>
+        </is>
+      </c>
+      <c r="D25" s="44" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E25" s="38" t="inlineStr">
         <is>
           <t>PWC National Pool of Hours [ONS]</t>
         </is>
       </c>
-      <c r="E25" s="38" t="inlineStr">
+      <c r="F25" s="40" t="inlineStr">
         <is>
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="F25" s="38" t="inlineStr">
+      <c r="G25" s="40" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G25" s="38" t="inlineStr">
+      <c r="H25" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H25" s="39" t="n">
+      <c r="I25" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="I25" s="39">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A25,'07 Aug 2026'!$K$3:$K$6,$D25)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A25,'21 Aug 2026'!$K$3:$K$7,$D25)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A25,'20 Sept 2026 '!$K$3:$K$14,$D25)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A25,'22 Sep 2026'!$K$3:$K$11,$D25)</f>
-        <v/>
-      </c>
-      <c r="J25" s="39">
-        <f>H25-I25</f>
-        <v/>
-      </c>
-      <c r="K25" s="38">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A25,'07 Aug 2026'!$K$3:$K$6,$D25)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A25,'21 Aug 2026'!$K$3:$K$7,$D25)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A25,'20 Sept 2026 '!$K$3:$K$14,$D25)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A25,'22 Sep 2026'!$K$3:$K$11,$D25)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L25" s="44" t="inlineStr">
+      <c r="J25" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A25,'07 Aug 2026'!$K$3:$K$6,$E25)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A25,'21 Aug 2026'!$K$3:$K$7,$E25)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A25,'20 Sept 2026 '!$K$3:$K$14,$E25)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A25,'22 Sep 2026'!$K$3:$K$11,$E25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="41">
+        <f>I25-J25</f>
+        <v/>
+      </c>
+      <c r="L25" s="45" t="inlineStr">
         <is>
           <t>Paid as a single 4 hr line - no break taken</t>
         </is>
@@ -1737,8 +1841,10 @@
       <c r="R25" s="24" t="n"/>
       <c r="S25" s="24" t="n"/>
       <c r="T25" s="24" t="n"/>
-    </row>
-    <row r="26" ht="30" customHeight="1" s="12">
+      <c r="U25" s="24" t="n"/>
+      <c r="V25" s="24" t="n"/>
+    </row>
+    <row r="26" ht="32" customHeight="1" s="12">
       <c r="A26" s="28" t="n">
         <v>46258</v>
       </c>
@@ -1747,47 +1853,48 @@
           <t>Mon</t>
         </is>
       </c>
-      <c r="C26" s="28" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D26" s="30" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E26" s="30" t="inlineStr">
         <is>
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="E26" s="29" t="inlineStr">
+      <c r="F26" s="29" t="inlineStr">
         <is>
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="F26" s="29" t="inlineStr">
+      <c r="G26" s="29" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G26" s="29" t="inlineStr">
+      <c r="H26" s="29" t="inlineStr">
         <is>
           <t>12:00-12:30</t>
         </is>
       </c>
-      <c r="H26" s="31" t="n">
+      <c r="I26" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="I26" s="31">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A26,'07 Aug 2026'!$K$3:$K$6,$D26)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A26,'21 Aug 2026'!$K$3:$K$7,$D26)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A26,'20 Sept 2026 '!$K$3:$K$14,$D26)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A26,'22 Sep 2026'!$K$3:$K$11,$D26)</f>
-        <v/>
-      </c>
-      <c r="J26" s="31">
-        <f>H26-I26</f>
-        <v/>
-      </c>
-      <c r="K26" s="29">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A26,'07 Aug 2026'!$K$3:$K$6,$D26)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A26,'21 Aug 2026'!$K$3:$K$7,$D26)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A26,'20 Sept 2026 '!$K$3:$K$14,$D26)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A26,'22 Sep 2026'!$K$3:$K$11,$D26)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L26" s="45" t="inlineStr">
-        <is>
-          <t>QUERY - claimed missing. PAID IN FULL in the 20 Sep 2026 run as 3.5 + 4.5 hrs. See Section A.</t>
+      <c r="J26" s="32">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A26,'07 Aug 2026'!$K$3:$K$6,$E26)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A26,'21 Aug 2026'!$K$3:$K$7,$E26)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A26,'20 Sept 2026 '!$K$3:$K$14,$E26)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A26,'22 Sep 2026'!$K$3:$K$11,$E26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="32">
+        <f>I26-J26</f>
+        <v/>
+      </c>
+      <c r="L26" s="46" t="inlineStr">
+        <is>
+          <t>QUERY - claimed missing. PAID IN FULL as 3.5 + 4.5 hrs. See Section A.</t>
         </is>
       </c>
       <c r="M26" s="24" t="n"/>
@@ -1798,57 +1905,60 @@
       <c r="R26" s="24" t="n"/>
       <c r="S26" s="24" t="n"/>
       <c r="T26" s="24" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="37" t="n">
+      <c r="U26" s="24" t="n"/>
+      <c r="V26" s="24" t="n"/>
+    </row>
+    <row r="27" ht="32" customHeight="1" s="12">
+      <c r="A27" s="47" t="n">
         <v>46259</v>
       </c>
-      <c r="B27" s="38" t="inlineStr">
+      <c r="B27" s="48" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C27" s="37" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D27" s="40" t="inlineStr">
+      <c r="C27" s="49" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D27" s="50" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E27" s="49" t="inlineStr">
         <is>
           <t>PWC National Pool of Hours [ONS]</t>
         </is>
       </c>
-      <c r="E27" s="38" t="inlineStr">
+      <c r="F27" s="48" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="F27" s="38" t="inlineStr">
+      <c r="G27" s="48" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G27" s="38" t="inlineStr">
+      <c r="H27" s="48" t="inlineStr">
         <is>
           <t>12:00-1:00</t>
         </is>
       </c>
-      <c r="H27" s="39" t="n">
+      <c r="I27" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="I27" s="39">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A27,'07 Aug 2026'!$K$3:$K$6,$D27)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A27,'21 Aug 2026'!$K$3:$K$7,$D27)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A27,'20 Sept 2026 '!$K$3:$K$14,$D27)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A27,'22 Sep 2026'!$K$3:$K$11,$D27)</f>
-        <v/>
-      </c>
-      <c r="J27" s="39">
-        <f>H27-I27</f>
-        <v/>
-      </c>
-      <c r="K27" s="38">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A27,'07 Aug 2026'!$K$3:$K$6,$D27)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A27,'21 Aug 2026'!$K$3:$K$7,$D27)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A27,'20 Sept 2026 '!$K$3:$K$14,$D27)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A27,'22 Sep 2026'!$K$3:$K$11,$D27)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L27" s="44" t="inlineStr">
-        <is>
-          <t>Paid as 4 + 4 hrs</t>
+      <c r="J27" s="51">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A27,'07 Aug 2026'!$K$3:$K$6,$E27)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A27,'21 Aug 2026'!$K$3:$K$7,$E27)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A27,'20 Sept 2026 '!$K$3:$K$14,$E27)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A27,'22 Sep 2026'!$K$3:$K$11,$E27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="51">
+        <f>I27-J27</f>
+        <v/>
+      </c>
+      <c r="L27" s="52" t="inlineStr">
+        <is>
+          <t>Paid as 4 + 4 hrs. Appears on the 22 Sep 2026 tab, not with the rest of this period - confirm the date actually paid.</t>
         </is>
       </c>
       <c r="M27" s="24" t="n"/>
@@ -1859,57 +1969,60 @@
       <c r="R27" s="24" t="n"/>
       <c r="S27" s="24" t="n"/>
       <c r="T27" s="24" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="37" t="n">
+      <c r="U27" s="24" t="n"/>
+      <c r="V27" s="24" t="n"/>
+    </row>
+    <row r="28" ht="32" customHeight="1" s="12">
+      <c r="A28" s="47" t="n">
         <v>46260</v>
       </c>
-      <c r="B28" s="38" t="inlineStr">
+      <c r="B28" s="48" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C28" s="37" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D28" s="40" t="inlineStr">
+      <c r="C28" s="49" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D28" s="50" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E28" s="49" t="inlineStr">
         <is>
           <t>PWC National Pool of Hours [ONS]</t>
         </is>
       </c>
-      <c r="E28" s="38" t="inlineStr">
+      <c r="F28" s="48" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="F28" s="38" t="inlineStr">
+      <c r="G28" s="48" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="G28" s="38" t="inlineStr">
+      <c r="H28" s="48" t="inlineStr">
         <is>
           <t>12:00-12:30</t>
         </is>
       </c>
-      <c r="H28" s="39" t="n">
+      <c r="I28" s="51" t="n">
         <v>7.5</v>
       </c>
-      <c r="I28" s="39">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A28,'07 Aug 2026'!$K$3:$K$6,$D28)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A28,'21 Aug 2026'!$K$3:$K$7,$D28)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A28,'20 Sept 2026 '!$K$3:$K$14,$D28)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A28,'22 Sep 2026'!$K$3:$K$11,$D28)</f>
-        <v/>
-      </c>
-      <c r="J28" s="39">
-        <f>H28-I28</f>
-        <v/>
-      </c>
-      <c r="K28" s="38">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A28,'07 Aug 2026'!$K$3:$K$6,$D28)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A28,'21 Aug 2026'!$K$3:$K$7,$D28)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A28,'20 Sept 2026 '!$K$3:$K$14,$D28)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A28,'22 Sep 2026'!$K$3:$K$11,$D28)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L28" s="44" t="inlineStr">
-        <is>
-          <t>Paid as 4 + 3.5 hrs</t>
+      <c r="J28" s="51">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A28,'07 Aug 2026'!$K$3:$K$6,$E28)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A28,'21 Aug 2026'!$K$3:$K$7,$E28)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A28,'20 Sept 2026 '!$K$3:$K$14,$E28)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A28,'22 Sep 2026'!$K$3:$K$11,$E28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="51">
+        <f>I28-J28</f>
+        <v/>
+      </c>
+      <c r="L28" s="52" t="inlineStr">
+        <is>
+          <t>Paid as 4 + 3.5 hrs. Appears on the 22 Sep 2026 tab, not with the rest of this period - confirm the date actually paid.</t>
         </is>
       </c>
       <c r="M28" s="24" t="n"/>
@@ -1920,57 +2033,60 @@
       <c r="R28" s="24" t="n"/>
       <c r="S28" s="24" t="n"/>
       <c r="T28" s="24" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="37" t="n">
+      <c r="U28" s="24" t="n"/>
+      <c r="V28" s="24" t="n"/>
+    </row>
+    <row r="29" ht="32" customHeight="1" s="12">
+      <c r="A29" s="47" t="n">
         <v>46261</v>
       </c>
-      <c r="B29" s="38" t="inlineStr">
+      <c r="B29" s="48" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C29" s="37" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D29" s="40" t="inlineStr">
+      <c r="C29" s="49" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D29" s="50" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E29" s="49" t="inlineStr">
         <is>
           <t>PWC National Pool of Hours [ONS]</t>
         </is>
       </c>
-      <c r="E29" s="38" t="inlineStr">
+      <c r="F29" s="48" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="F29" s="38" t="inlineStr">
+      <c r="G29" s="48" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G29" s="38" t="inlineStr">
+      <c r="H29" s="48" t="inlineStr">
         <is>
           <t>12:00-1:00</t>
         </is>
       </c>
-      <c r="H29" s="39" t="n">
+      <c r="I29" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="I29" s="39">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A29,'07 Aug 2026'!$K$3:$K$6,$D29)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A29,'21 Aug 2026'!$K$3:$K$7,$D29)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A29,'20 Sept 2026 '!$K$3:$K$14,$D29)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A29,'22 Sep 2026'!$K$3:$K$11,$D29)</f>
-        <v/>
-      </c>
-      <c r="J29" s="39">
-        <f>H29-I29</f>
-        <v/>
-      </c>
-      <c r="K29" s="38">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A29,'07 Aug 2026'!$K$3:$K$6,$D29)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A29,'21 Aug 2026'!$K$3:$K$7,$D29)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A29,'20 Sept 2026 '!$K$3:$K$14,$D29)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A29,'22 Sep 2026'!$K$3:$K$11,$D29)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L29" s="44" t="inlineStr">
-        <is>
-          <t>Paid as 4 + 4 hrs</t>
+      <c r="J29" s="51">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A29,'07 Aug 2026'!$K$3:$K$6,$E29)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A29,'21 Aug 2026'!$K$3:$K$7,$E29)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A29,'20 Sept 2026 '!$K$3:$K$14,$E29)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A29,'22 Sep 2026'!$K$3:$K$11,$E29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="51">
+        <f>I29-J29</f>
+        <v/>
+      </c>
+      <c r="L29" s="52" t="inlineStr">
+        <is>
+          <t>Paid as 4 + 4 hrs. Appears on the 22 Sep 2026 tab, not with the rest of this period - confirm the date actually paid.</t>
         </is>
       </c>
       <c r="M29" s="24" t="n"/>
@@ -1981,8 +2097,10 @@
       <c r="R29" s="24" t="n"/>
       <c r="S29" s="24" t="n"/>
       <c r="T29" s="24" t="n"/>
-    </row>
-    <row r="30" ht="30" customHeight="1" s="12">
+      <c r="U29" s="24" t="n"/>
+      <c r="V29" s="24" t="n"/>
+    </row>
+    <row r="30" ht="32" customHeight="1" s="12">
       <c r="A30" s="28" t="n">
         <v>46262</v>
       </c>
@@ -1991,47 +2109,48 @@
           <t>Fri</t>
         </is>
       </c>
-      <c r="C30" s="28" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D30" s="30" t="inlineStr">
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="E30" s="29" t="inlineStr">
+      <c r="F30" s="29" t="inlineStr">
         <is>
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="F30" s="29" t="inlineStr">
+      <c r="G30" s="29" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G30" s="29" t="inlineStr">
+      <c r="H30" s="29" t="inlineStr">
         <is>
           <t>12:00-12:30</t>
         </is>
       </c>
-      <c r="H30" s="31" t="n">
+      <c r="I30" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="I30" s="31">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A30,'07 Aug 2026'!$K$3:$K$6,$D30)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A30,'21 Aug 2026'!$K$3:$K$7,$D30)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A30,'20 Sept 2026 '!$K$3:$K$14,$D30)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A30,'22 Sep 2026'!$K$3:$K$11,$D30)</f>
-        <v/>
-      </c>
-      <c r="J30" s="31">
-        <f>H30-I30</f>
-        <v/>
-      </c>
-      <c r="K30" s="29">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A30,'07 Aug 2026'!$K$3:$K$6,$D30)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A30,'21 Aug 2026'!$K$3:$K$7,$D30)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A30,'20 Sept 2026 '!$K$3:$K$14,$D30)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A30,'22 Sep 2026'!$K$3:$K$11,$D30)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L30" s="45" t="inlineStr">
-        <is>
-          <t>QUERY - claimed missing. PAID IN FULL in the 20 Sep 2026 run as 3.5 + 4.5 hrs. See Section A.</t>
+      <c r="J30" s="32">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A30,'07 Aug 2026'!$K$3:$K$6,$E30)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A30,'21 Aug 2026'!$K$3:$K$7,$E30)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A30,'20 Sept 2026 '!$K$3:$K$14,$E30)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A30,'22 Sep 2026'!$K$3:$K$11,$E30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="32">
+        <f>I30-J30</f>
+        <v/>
+      </c>
+      <c r="L30" s="46" t="inlineStr">
+        <is>
+          <t>QUERY - claimed missing. PAID IN FULL as 3.5 + 4.5 hrs. See Section A.</t>
         </is>
       </c>
       <c r="M30" s="24" t="n"/>
@@ -2042,55 +2161,58 @@
       <c r="R30" s="24" t="n"/>
       <c r="S30" s="24" t="n"/>
       <c r="T30" s="24" t="n"/>
+      <c r="U30" s="24" t="n"/>
+      <c r="V30" s="24" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="37" t="n">
+      <c r="A31" s="39" t="n">
         <v>46265</v>
       </c>
-      <c r="B31" s="38" t="inlineStr">
+      <c r="B31" s="40" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="C31" s="37" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D31" s="40" t="inlineStr">
+      <c r="C31" s="38" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D31" s="44" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E31" s="38" t="inlineStr">
         <is>
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="E31" s="38" t="inlineStr">
+      <c r="F31" s="40" t="inlineStr">
         <is>
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="F31" s="38" t="inlineStr">
+      <c r="G31" s="40" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G31" s="38" t="inlineStr">
+      <c r="H31" s="40" t="inlineStr">
         <is>
           <t>12:00-12:30</t>
         </is>
       </c>
-      <c r="H31" s="39" t="n">
+      <c r="I31" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="I31" s="39">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A31,'07 Aug 2026'!$K$3:$K$6,$D31)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A31,'21 Aug 2026'!$K$3:$K$7,$D31)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A31,'20 Sept 2026 '!$K$3:$K$14,$D31)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A31,'22 Sep 2026'!$K$3:$K$11,$D31)</f>
-        <v/>
-      </c>
-      <c r="J31" s="39">
-        <f>H31-I31</f>
-        <v/>
-      </c>
-      <c r="K31" s="38">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A31,'07 Aug 2026'!$K$3:$K$6,$D31)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A31,'21 Aug 2026'!$K$3:$K$7,$D31)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A31,'20 Sept 2026 '!$K$3:$K$14,$D31)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A31,'22 Sep 2026'!$K$3:$K$11,$D31)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L31" s="44" t="inlineStr">
+      <c r="J31" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A31,'07 Aug 2026'!$K$3:$K$6,$E31)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A31,'21 Aug 2026'!$K$3:$K$7,$E31)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A31,'20 Sept 2026 '!$K$3:$K$14,$E31)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A31,'22 Sep 2026'!$K$3:$K$11,$E31)</f>
+        <v/>
+      </c>
+      <c r="K31" s="41">
+        <f>I31-J31</f>
+        <v/>
+      </c>
+      <c r="L31" s="45" t="inlineStr">
         <is>
           <t>Paid as 3.5 + 4.5 hrs</t>
         </is>
@@ -2103,55 +2225,58 @@
       <c r="R31" s="24" t="n"/>
       <c r="S31" s="24" t="n"/>
       <c r="T31" s="24" t="n"/>
+      <c r="U31" s="24" t="n"/>
+      <c r="V31" s="24" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="37" t="n">
+      <c r="A32" s="39" t="n">
         <v>46266</v>
       </c>
-      <c r="B32" s="38" t="inlineStr">
+      <c r="B32" s="40" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C32" s="37" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D32" s="40" t="inlineStr">
+      <c r="C32" s="38" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D32" s="44" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E32" s="38" t="inlineStr">
         <is>
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="E32" s="38" t="inlineStr">
+      <c r="F32" s="40" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="F32" s="38" t="inlineStr">
+      <c r="G32" s="40" t="inlineStr">
         <is>
           <t>5:30 PM</t>
         </is>
       </c>
-      <c r="G32" s="38" t="inlineStr">
+      <c r="H32" s="40" t="inlineStr">
         <is>
           <t>12:00-12:30</t>
         </is>
       </c>
-      <c r="H32" s="39" t="n">
+      <c r="I32" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="I32" s="39">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A32,'07 Aug 2026'!$K$3:$K$6,$D32)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A32,'21 Aug 2026'!$K$3:$K$7,$D32)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A32,'20 Sept 2026 '!$K$3:$K$14,$D32)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A32,'22 Sep 2026'!$K$3:$K$11,$D32)</f>
-        <v/>
-      </c>
-      <c r="J32" s="39">
-        <f>H32-I32</f>
-        <v/>
-      </c>
-      <c r="K32" s="38">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A32,'07 Aug 2026'!$K$3:$K$6,$D32)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A32,'21 Aug 2026'!$K$3:$K$7,$D32)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A32,'20 Sept 2026 '!$K$3:$K$14,$D32)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A32,'22 Sep 2026'!$K$3:$K$11,$D32)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L32" s="44" t="inlineStr">
+      <c r="J32" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A32,'07 Aug 2026'!$K$3:$K$6,$E32)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A32,'21 Aug 2026'!$K$3:$K$7,$E32)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A32,'20 Sept 2026 '!$K$3:$K$14,$E32)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A32,'22 Sep 2026'!$K$3:$K$11,$E32)</f>
+        <v/>
+      </c>
+      <c r="K32" s="41">
+        <f>I32-J32</f>
+        <v/>
+      </c>
+      <c r="L32" s="45" t="inlineStr">
         <is>
           <t>Paid as 3 + 5 hrs</t>
         </is>
@@ -2164,55 +2289,58 @@
       <c r="R32" s="24" t="n"/>
       <c r="S32" s="24" t="n"/>
       <c r="T32" s="24" t="n"/>
+      <c r="U32" s="24" t="n"/>
+      <c r="V32" s="24" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="37" t="n">
+      <c r="A33" s="39" t="n">
         <v>46267</v>
       </c>
-      <c r="B33" s="38" t="inlineStr">
+      <c r="B33" s="40" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C33" s="37" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D33" s="40" t="inlineStr">
+      <c r="C33" s="38" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D33" s="44" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E33" s="38" t="inlineStr">
         <is>
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="E33" s="38" t="inlineStr">
+      <c r="F33" s="40" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="F33" s="38" t="inlineStr">
+      <c r="G33" s="40" t="inlineStr">
         <is>
           <t>5:30 PM</t>
         </is>
       </c>
-      <c r="G33" s="38" t="inlineStr">
+      <c r="H33" s="40" t="inlineStr">
         <is>
           <t>12:00-12:30</t>
         </is>
       </c>
-      <c r="H33" s="39" t="n">
+      <c r="I33" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="I33" s="39">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A33,'07 Aug 2026'!$K$3:$K$6,$D33)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A33,'21 Aug 2026'!$K$3:$K$7,$D33)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A33,'20 Sept 2026 '!$K$3:$K$14,$D33)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A33,'22 Sep 2026'!$K$3:$K$11,$D33)</f>
-        <v/>
-      </c>
-      <c r="J33" s="39">
-        <f>H33-I33</f>
-        <v/>
-      </c>
-      <c r="K33" s="38">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A33,'07 Aug 2026'!$K$3:$K$6,$D33)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A33,'21 Aug 2026'!$K$3:$K$7,$D33)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A33,'20 Sept 2026 '!$K$3:$K$14,$D33)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A33,'22 Sep 2026'!$K$3:$K$11,$D33)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L33" s="44" t="inlineStr">
+      <c r="J33" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A33,'07 Aug 2026'!$K$3:$K$6,$E33)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A33,'21 Aug 2026'!$K$3:$K$7,$E33)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A33,'20 Sept 2026 '!$K$3:$K$14,$E33)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A33,'22 Sep 2026'!$K$3:$K$11,$E33)</f>
+        <v/>
+      </c>
+      <c r="K33" s="41">
+        <f>I33-J33</f>
+        <v/>
+      </c>
+      <c r="L33" s="45" t="inlineStr">
         <is>
           <t>Paid as 3 + 5 hrs</t>
         </is>
@@ -2225,55 +2353,58 @@
       <c r="R33" s="24" t="n"/>
       <c r="S33" s="24" t="n"/>
       <c r="T33" s="24" t="n"/>
+      <c r="U33" s="24" t="n"/>
+      <c r="V33" s="24" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="37" t="n">
+      <c r="A34" s="39" t="n">
         <v>46269</v>
       </c>
-      <c r="B34" s="38" t="inlineStr">
+      <c r="B34" s="40" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C34" s="37" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D34" s="40" t="inlineStr">
+      <c r="C34" s="38" t="inlineStr">
+        <is>
+          <t>22/08/2026 - 04/09/2026</t>
+        </is>
+      </c>
+      <c r="D34" s="44" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E34" s="38" t="inlineStr">
         <is>
           <t>DTTL Mel Tech FT 1 [ONS]</t>
         </is>
       </c>
-      <c r="E34" s="38" t="inlineStr">
+      <c r="F34" s="40" t="inlineStr">
         <is>
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="F34" s="38" t="inlineStr">
+      <c r="G34" s="40" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G34" s="38" t="inlineStr">
+      <c r="H34" s="40" t="inlineStr">
         <is>
           <t>12:00-12:30</t>
         </is>
       </c>
-      <c r="H34" s="39" t="n">
+      <c r="I34" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="I34" s="39">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A34,'07 Aug 2026'!$K$3:$K$6,$D34)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A34,'21 Aug 2026'!$K$3:$K$7,$D34)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A34,'20 Sept 2026 '!$K$3:$K$14,$D34)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A34,'22 Sep 2026'!$K$3:$K$11,$D34)</f>
-        <v/>
-      </c>
-      <c r="J34" s="39">
-        <f>H34-I34</f>
-        <v/>
-      </c>
-      <c r="K34" s="38">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A34,'07 Aug 2026'!$K$3:$K$6,$D34)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A34,'21 Aug 2026'!$K$3:$K$7,$D34)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A34,'20 Sept 2026 '!$K$3:$K$14,$D34)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A34,'22 Sep 2026'!$K$3:$K$11,$D34)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L34" s="44" t="inlineStr">
+      <c r="J34" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A34,'07 Aug 2026'!$K$3:$K$6,$E34)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A34,'21 Aug 2026'!$K$3:$K$7,$E34)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A34,'20 Sept 2026 '!$K$3:$K$14,$E34)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A34,'22 Sep 2026'!$K$3:$K$11,$E34)</f>
+        <v/>
+      </c>
+      <c r="K34" s="41">
+        <f>I34-J34</f>
+        <v/>
+      </c>
+      <c r="L34" s="45" t="inlineStr">
         <is>
           <t>Paid as 3.5 + 4.5 hrs</t>
         </is>
@@ -2286,55 +2417,58 @@
       <c r="R34" s="24" t="n"/>
       <c r="S34" s="24" t="n"/>
       <c r="T34" s="24" t="n"/>
+      <c r="U34" s="24" t="n"/>
+      <c r="V34" s="24" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="37" t="n">
+      <c r="A35" s="39" t="n">
         <v>46275</v>
       </c>
-      <c r="B35" s="38" t="inlineStr">
+      <c r="B35" s="40" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C35" s="37" t="n">
-        <v>46283</v>
-      </c>
-      <c r="D35" s="40" t="inlineStr">
+      <c r="C35" s="38" t="inlineStr">
+        <is>
+          <t>05/09/2026 - 18/09/2026</t>
+        </is>
+      </c>
+      <c r="D35" s="44" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E35" s="38" t="inlineStr">
         <is>
           <t>PWC National Pool of Hours [ONS]</t>
         </is>
       </c>
-      <c r="E35" s="38" t="inlineStr">
+      <c r="F35" s="40" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="F35" s="38" t="inlineStr">
+      <c r="G35" s="40" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G35" s="38" t="inlineStr">
+      <c r="H35" s="40" t="inlineStr">
         <is>
           <t>12:00-1:00</t>
         </is>
       </c>
-      <c r="H35" s="39" t="n">
+      <c r="I35" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="I35" s="39">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A35,'07 Aug 2026'!$K$3:$K$6,$D35)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A35,'21 Aug 2026'!$K$3:$K$7,$D35)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A35,'20 Sept 2026 '!$K$3:$K$14,$D35)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A35,'22 Sep 2026'!$K$3:$K$11,$D35)</f>
-        <v/>
-      </c>
-      <c r="J35" s="39">
-        <f>H35-I35</f>
-        <v/>
-      </c>
-      <c r="K35" s="38">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A35,'07 Aug 2026'!$K$3:$K$6,$D35)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A35,'21 Aug 2026'!$K$3:$K$7,$D35)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A35,'20 Sept 2026 '!$K$3:$K$14,$D35)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A35,'22 Sep 2026'!$K$3:$K$11,$D35)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L35" s="44" t="inlineStr">
+      <c r="J35" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A35,'07 Aug 2026'!$K$3:$K$6,$E35)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A35,'21 Aug 2026'!$K$3:$K$7,$E35)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A35,'20 Sept 2026 '!$K$3:$K$14,$E35)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A35,'22 Sep 2026'!$K$3:$K$11,$E35)</f>
+        <v/>
+      </c>
+      <c r="K35" s="41">
+        <f>I35-J35</f>
+        <v/>
+      </c>
+      <c r="L35" s="45" t="inlineStr">
         <is>
           <t>Paid as 4 + 4 hrs</t>
         </is>
@@ -2347,55 +2481,58 @@
       <c r="R35" s="24" t="n"/>
       <c r="S35" s="24" t="n"/>
       <c r="T35" s="24" t="n"/>
+      <c r="U35" s="24" t="n"/>
+      <c r="V35" s="24" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="37" t="n">
+      <c r="A36" s="39" t="n">
         <v>46282</v>
       </c>
-      <c r="B36" s="38" t="inlineStr">
+      <c r="B36" s="40" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C36" s="37" t="n">
-        <v>46283</v>
-      </c>
-      <c r="D36" s="40" t="inlineStr">
+      <c r="C36" s="38" t="inlineStr">
+        <is>
+          <t>05/09/2026 - 18/09/2026</t>
+        </is>
+      </c>
+      <c r="D36" s="44" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E36" s="38" t="inlineStr">
         <is>
           <t>Aware Super AV Maintenance [ONS]</t>
         </is>
       </c>
-      <c r="E36" s="38" t="inlineStr">
+      <c r="F36" s="40" t="inlineStr">
         <is>
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="F36" s="38" t="inlineStr">
+      <c r="G36" s="40" t="inlineStr">
         <is>
           <t>3:30 PM</t>
         </is>
       </c>
-      <c r="G36" s="38" t="inlineStr">
+      <c r="H36" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H36" s="39" t="n">
+      <c r="I36" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="I36" s="39">
-        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A36,'07 Aug 2026'!$K$3:$K$6,$D36)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A36,'21 Aug 2026'!$K$3:$K$7,$D36)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A36,'20 Sept 2026 '!$K$3:$K$14,$D36)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A36,'22 Sep 2026'!$K$3:$K$11,$D36)</f>
-        <v/>
-      </c>
-      <c r="J36" s="39">
-        <f>H36-I36</f>
-        <v/>
-      </c>
-      <c r="K36" s="38">
-        <f>IF(SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A36,'07 Aug 2026'!$K$3:$K$6,$D36)&lt;&gt;0,"07 Aug 2026",IF(SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A36,'21 Aug 2026'!$K$3:$K$7,$D36)&lt;&gt;0,"21 Aug 2026",IF(SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A36,'20 Sept 2026 '!$K$3:$K$14,$D36)&lt;&gt;0,"20 Sep 2026",IF(SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A36,'22 Sep 2026'!$K$3:$K$11,$D36)&lt;&gt;0,"22 Sep 2026","NOT PAID"))))</f>
-        <v/>
-      </c>
-      <c r="L36" s="44" t="inlineStr">
+      <c r="J36" s="41">
+        <f>SUMIFS('07 Aug 2026'!$G$3:$G$6,'07 Aug 2026'!$M$3:$M$6,$A36,'07 Aug 2026'!$K$3:$K$6,$E36)+SUMIFS('21 Aug 2026'!$G$3:$G$7,'21 Aug 2026'!$M$3:$M$7,$A36,'21 Aug 2026'!$K$3:$K$7,$E36)+SUMIFS('20 Sept 2026 '!$G$3:$G$14,'20 Sept 2026 '!$M$3:$M$14,$A36,'20 Sept 2026 '!$K$3:$K$14,$E36)+SUMIFS('22 Sep 2026'!$G$3:$G$11,'22 Sep 2026'!$M$3:$M$11,$A36,'22 Sep 2026'!$K$3:$K$11,$E36)</f>
+        <v/>
+      </c>
+      <c r="K36" s="41">
+        <f>I36-J36</f>
+        <v/>
+      </c>
+      <c r="L36" s="45" t="inlineStr">
         <is>
           <t>Paid as a single 4 hr line - no break taken</t>
         </is>
@@ -2408,23 +2545,22 @@
       <c r="R36" s="24" t="n"/>
       <c r="S36" s="24" t="n"/>
       <c r="T36" s="24" t="n"/>
+      <c r="U36" s="24" t="n"/>
+      <c r="V36" s="24" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="41" t="inlineStr">
+      <c r="A37" s="42" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B37" s="41" t="n"/>
-      <c r="C37" s="41" t="n"/>
-      <c r="D37" s="41" t="n"/>
-      <c r="E37" s="41" t="n"/>
-      <c r="F37" s="41" t="n"/>
-      <c r="G37" s="41" t="n"/>
-      <c r="H37" s="43">
-        <f>SUM(H21:H36)</f>
-        <v/>
-      </c>
+      <c r="B37" s="42" t="n"/>
+      <c r="C37" s="42" t="n"/>
+      <c r="D37" s="42" t="n"/>
+      <c r="E37" s="42" t="n"/>
+      <c r="F37" s="42" t="n"/>
+      <c r="G37" s="42" t="n"/>
+      <c r="H37" s="42" t="n"/>
       <c r="I37" s="43">
         <f>SUM(I21:I36)</f>
         <v/>
@@ -2433,11 +2569,14 @@
         <f>SUM(J21:J36)</f>
         <v/>
       </c>
-      <c r="K37" s="41">
-        <f>IF(ROUND(J37,2)=0,"HOURS AGREE","VARIANCE")</f>
-        <v/>
-      </c>
-      <c r="L37" s="41" t="n"/>
+      <c r="K37" s="43">
+        <f>SUM(K21:K36)</f>
+        <v/>
+      </c>
+      <c r="L37" s="42">
+        <f>IF(ROUND(K37,2)=0,"HOURS AGREE","VARIANCE")</f>
+        <v/>
+      </c>
       <c r="M37" s="24" t="n"/>
       <c r="N37" s="24" t="n"/>
       <c r="O37" s="24" t="n"/>
@@ -2446,6 +2585,8 @@
       <c r="R37" s="24" t="n"/>
       <c r="S37" s="24" t="n"/>
       <c r="T37" s="24" t="n"/>
+      <c r="U37" s="24" t="n"/>
+      <c r="V37" s="24" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="24" t="n"/>
@@ -2468,24 +2609,26 @@
       <c r="R38" s="24" t="n"/>
       <c r="S38" s="24" t="n"/>
       <c r="T38" s="24" t="n"/>
+      <c r="U38" s="24" t="n"/>
+      <c r="V38" s="24" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="36" t="inlineStr">
-        <is>
-          <t>D.  ADJUSTMENT LINES ON THE PAY RUNS  -  why two lines on the 21 Aug 2026 run carry no work date</t>
-        </is>
-      </c>
-      <c r="B39" s="36" t="n"/>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="36" t="n"/>
-      <c r="E39" s="36" t="n"/>
-      <c r="F39" s="36" t="n"/>
-      <c r="G39" s="36" t="n"/>
-      <c r="H39" s="36" t="n"/>
-      <c r="I39" s="36" t="n"/>
-      <c r="J39" s="36" t="n"/>
-      <c r="K39" s="36" t="n"/>
-      <c r="L39" s="36" t="n"/>
+      <c r="A39" s="37" t="inlineStr">
+        <is>
+          <t>D.  ADJUSTMENT LINES  -  why two lines paid on 25/08/2026 carry no work date</t>
+        </is>
+      </c>
+      <c r="B39" s="37" t="n"/>
+      <c r="C39" s="37" t="n"/>
+      <c r="D39" s="37" t="n"/>
+      <c r="E39" s="37" t="n"/>
+      <c r="F39" s="37" t="n"/>
+      <c r="G39" s="37" t="n"/>
+      <c r="H39" s="37" t="n"/>
+      <c r="I39" s="37" t="n"/>
+      <c r="J39" s="37" t="n"/>
+      <c r="K39" s="37" t="n"/>
+      <c r="L39" s="37" t="n"/>
       <c r="M39" s="24" t="n"/>
       <c r="N39" s="24" t="n"/>
       <c r="O39" s="24" t="n"/>
@@ -2494,8 +2637,10 @@
       <c r="R39" s="24" t="n"/>
       <c r="S39" s="24" t="n"/>
       <c r="T39" s="24" t="n"/>
-    </row>
-    <row r="40" ht="30" customHeight="1" s="12">
+      <c r="U39" s="24" t="n"/>
+      <c r="V39" s="24" t="n"/>
+    </row>
+    <row r="40" ht="32" customHeight="1" s="12">
       <c r="A40" s="27" t="inlineStr">
         <is>
           <t>Item</t>
@@ -2503,7 +2648,7 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>Pay Run</t>
+          <t>Paid On</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
@@ -2532,25 +2677,25 @@
       <c r="R40" s="24" t="n"/>
       <c r="S40" s="24" t="n"/>
       <c r="T40" s="24" t="n"/>
+      <c r="U40" s="24" t="n"/>
+      <c r="V40" s="24" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="40" t="inlineStr">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>Reversal line</t>
         </is>
       </c>
-      <c r="B41" s="40" t="inlineStr">
-        <is>
-          <t>21 Aug 2026</t>
-        </is>
-      </c>
-      <c r="C41" s="39">
+      <c r="B41" s="39" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C41" s="41">
         <f>'21 Aug 2026'!G3</f>
         <v/>
       </c>
-      <c r="D41" s="44" t="inlineStr">
-        <is>
-          <t>Reverses the 16 hrs originally paid for the fortnight ending 07/08/2026</t>
+      <c r="D41" s="45" t="inlineStr">
+        <is>
+          <t>Reverses the 16 hrs first paid for the period 25/07/2026 - 07/08/2026</t>
         </is>
       </c>
       <c r="E41" s="24" t="n"/>
@@ -2569,25 +2714,25 @@
       <c r="R41" s="24" t="n"/>
       <c r="S41" s="24" t="n"/>
       <c r="T41" s="24" t="n"/>
+      <c r="U41" s="24" t="n"/>
+      <c r="V41" s="24" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="40" t="inlineStr">
+      <c r="A42" s="38" t="inlineStr">
         <is>
           <t>Re-payment line</t>
         </is>
       </c>
-      <c r="B42" s="40" t="inlineStr">
-        <is>
-          <t>21 Aug 2026</t>
-        </is>
-      </c>
-      <c r="C42" s="39">
+      <c r="B42" s="39" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C42" s="41">
         <f>'21 Aug 2026'!G4</f>
         <v/>
       </c>
-      <c r="D42" s="44" t="inlineStr">
-        <is>
-          <t>Re-pays those same 16 hrs. These two lines exist to correct the pay rate used, not the hours</t>
+      <c r="D42" s="45" t="inlineStr">
+        <is>
+          <t>Re-pays those same 16 hrs. These lines correct the pay rate, not the hours</t>
         </is>
       </c>
       <c r="E42" s="24" t="n"/>
@@ -2606,25 +2751,25 @@
       <c r="R42" s="24" t="n"/>
       <c r="S42" s="24" t="n"/>
       <c r="T42" s="24" t="n"/>
+      <c r="U42" s="24" t="n"/>
+      <c r="V42" s="24" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="41" t="inlineStr">
+      <c r="A43" s="42" t="inlineStr">
         <is>
           <t>NET EFFECT ON HOURS</t>
         </is>
       </c>
-      <c r="B43" s="41" t="inlineStr">
-        <is>
-          <t>21 Aug 2026</t>
-        </is>
+      <c r="B43" s="53" t="n">
+        <v>46259</v>
       </c>
       <c r="C43" s="43">
         <f>C41+C42</f>
         <v/>
       </c>
-      <c r="D43" s="46" t="inlineStr">
-        <is>
-          <t>Nil. No hours were added or removed - the 16 hrs remain counted once, in the 07 Aug 2026 run</t>
+      <c r="D43" s="54" t="inlineStr">
+        <is>
+          <t>Nil - the 16 hrs remain counted once, in the period ending 07/08/2026</t>
         </is>
       </c>
       <c r="E43" s="24" t="n"/>
@@ -2643,6 +2788,8 @@
       <c r="R43" s="24" t="n"/>
       <c r="S43" s="24" t="n"/>
       <c r="T43" s="24" t="n"/>
+      <c r="U43" s="24" t="n"/>
+      <c r="V43" s="24" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="24" t="n"/>
@@ -2665,24 +2812,22 @@
       <c r="R44" s="24" t="n"/>
       <c r="S44" s="24" t="n"/>
       <c r="T44" s="24" t="n"/>
+      <c r="U44" s="24" t="n"/>
+      <c r="V44" s="24" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="36" t="inlineStr">
-        <is>
-          <t>E.  COMPLETENESS CHECK  -  proves no paid hours sit outside this reconciliation</t>
-        </is>
-      </c>
-      <c r="B45" s="36" t="n"/>
-      <c r="C45" s="36" t="n"/>
-      <c r="D45" s="36" t="n"/>
-      <c r="E45" s="36" t="n"/>
-      <c r="F45" s="36" t="n"/>
-      <c r="G45" s="36" t="n"/>
-      <c r="H45" s="36" t="n"/>
-      <c r="I45" s="36" t="n"/>
-      <c r="J45" s="36" t="n"/>
-      <c r="K45" s="36" t="n"/>
-      <c r="L45" s="36" t="n"/>
+      <c r="A45" s="24" t="n"/>
+      <c r="B45" s="24" t="n"/>
+      <c r="C45" s="24" t="n"/>
+      <c r="D45" s="24" t="n"/>
+      <c r="E45" s="24" t="n"/>
+      <c r="F45" s="24" t="n"/>
+      <c r="G45" s="24" t="n"/>
+      <c r="H45" s="24" t="n"/>
+      <c r="I45" s="24" t="n"/>
+      <c r="J45" s="24" t="n"/>
+      <c r="K45" s="24" t="n"/>
+      <c r="L45" s="24" t="n"/>
       <c r="M45" s="24" t="n"/>
       <c r="N45" s="24" t="n"/>
       <c r="O45" s="24" t="n"/>
@@ -2691,23 +2836,13 @@
       <c r="R45" s="24" t="n"/>
       <c r="S45" s="24" t="n"/>
       <c r="T45" s="24" t="n"/>
-    </row>
-    <row r="46" ht="30" customHeight="1" s="12">
-      <c r="A46" s="27" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B46" s="27" t="inlineStr">
-        <is>
-          <t>Hours</t>
-        </is>
-      </c>
-      <c r="C46" s="27" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
+      <c r="U45" s="24" t="n"/>
+      <c r="V45" s="24" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="24" t="n"/>
+      <c r="B46" s="24" t="n"/>
+      <c r="C46" s="24" t="n"/>
       <c r="D46" s="24" t="n"/>
       <c r="E46" s="24" t="n"/>
       <c r="F46" s="24" t="n"/>
@@ -2725,18 +2860,13 @@
       <c r="R46" s="24" t="n"/>
       <c r="S46" s="24" t="n"/>
       <c r="T46" s="24" t="n"/>
+      <c r="U46" s="24" t="n"/>
+      <c r="V46" s="24" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="40" t="inlineStr">
-        <is>
-          <t>Total hours on all four pay-run tabs (including the two adjustment lines)</t>
-        </is>
-      </c>
-      <c r="B47" s="39">
-        <f>SUM('07 Aug 2026'!$G$3:$G$6)+SUM('21 Aug 2026'!$G$3:$G$7)+SUM('20 Sept 2026 '!$G$3:$G$14)+SUM('22 Sep 2026'!$G$3:$G$11)</f>
-        <v/>
-      </c>
-      <c r="C47" s="44" t="inlineStr"/>
+      <c r="A47" s="24" t="n"/>
+      <c r="B47" s="24" t="n"/>
+      <c r="C47" s="24" t="n"/>
       <c r="D47" s="24" t="n"/>
       <c r="E47" s="24" t="n"/>
       <c r="F47" s="24" t="n"/>
@@ -2754,27 +2884,26 @@
       <c r="R47" s="24" t="n"/>
       <c r="S47" s="24" t="n"/>
       <c r="T47" s="24" t="n"/>
+      <c r="U47" s="24" t="n"/>
+      <c r="V47" s="24" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="40" t="inlineStr">
-        <is>
-          <t>Total paid hours matched to a timesheet line in Section C</t>
-        </is>
-      </c>
-      <c r="B48" s="39">
-        <f>I37</f>
-        <v/>
-      </c>
-      <c r="C48" s="44" t="inlineStr"/>
-      <c r="D48" s="24" t="n"/>
-      <c r="E48" s="24" t="n"/>
-      <c r="F48" s="24" t="n"/>
-      <c r="G48" s="24" t="n"/>
-      <c r="H48" s="24" t="n"/>
-      <c r="I48" s="24" t="n"/>
-      <c r="J48" s="24" t="n"/>
-      <c r="K48" s="24" t="n"/>
-      <c r="L48" s="24" t="n"/>
+      <c r="A48" s="37" t="inlineStr">
+        <is>
+          <t>E.  COMPLETENESS CHECK  -  proves no paid hours sit outside this reconciliation</t>
+        </is>
+      </c>
+      <c r="B48" s="37" t="n"/>
+      <c r="C48" s="37" t="n"/>
+      <c r="D48" s="37" t="n"/>
+      <c r="E48" s="37" t="n"/>
+      <c r="F48" s="37" t="n"/>
+      <c r="G48" s="37" t="n"/>
+      <c r="H48" s="37" t="n"/>
+      <c r="I48" s="37" t="n"/>
+      <c r="J48" s="37" t="n"/>
+      <c r="K48" s="37" t="n"/>
+      <c r="L48" s="37" t="n"/>
       <c r="M48" s="24" t="n"/>
       <c r="N48" s="24" t="n"/>
       <c r="O48" s="24" t="n"/>
@@ -2783,20 +2912,24 @@
       <c r="R48" s="24" t="n"/>
       <c r="S48" s="24" t="n"/>
       <c r="T48" s="24" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="40" t="inlineStr">
-        <is>
-          <t>Unmatched paid hours</t>
-        </is>
-      </c>
-      <c r="B49" s="39">
-        <f>B47-B48</f>
-        <v/>
-      </c>
-      <c r="C49" s="44">
-        <f>IF(ROUND(B49,2)=0,"OK - every paid hour ties to a timesheet line","INVESTIGATE - unmatched paid hours")</f>
-        <v/>
+      <c r="U48" s="24" t="n"/>
+      <c r="V48" s="24" t="n"/>
+    </row>
+    <row r="49" ht="32" customHeight="1" s="12">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="C49" s="27" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
       </c>
       <c r="D49" s="24" t="n"/>
       <c r="E49" s="24" t="n"/>
@@ -2815,18 +2948,20 @@
       <c r="R49" s="24" t="n"/>
       <c r="S49" s="24" t="n"/>
       <c r="T49" s="24" t="n"/>
+      <c r="U49" s="24" t="n"/>
+      <c r="V49" s="24" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="40" t="inlineStr">
-        <is>
-          <t>Total timesheet hours per the screenshots</t>
-        </is>
-      </c>
-      <c r="B50" s="39">
-        <f>H37</f>
-        <v/>
-      </c>
-      <c r="C50" s="44" t="inlineStr"/>
+      <c r="A50" s="38" t="inlineStr">
+        <is>
+          <t>Total hours on all four pay-run tabs (including the two rate-correction lines)</t>
+        </is>
+      </c>
+      <c r="B50" s="41">
+        <f>SUM('07 Aug 2026'!$G$3:$G$6)+SUM('21 Aug 2026'!$G$3:$G$7)+SUM('20 Sept 2026 '!$G$3:$G$14)+SUM('22 Sep 2026'!$G$3:$G$11)</f>
+        <v/>
+      </c>
+      <c r="C50" s="45" t="inlineStr"/>
       <c r="D50" s="24" t="n"/>
       <c r="E50" s="24" t="n"/>
       <c r="F50" s="24" t="n"/>
@@ -2844,21 +2979,20 @@
       <c r="R50" s="24" t="n"/>
       <c r="S50" s="24" t="n"/>
       <c r="T50" s="24" t="n"/>
+      <c r="U50" s="24" t="n"/>
+      <c r="V50" s="24" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="41" t="inlineStr">
-        <is>
-          <t>HOURS VARIANCE (timesheet less paid)</t>
-        </is>
-      </c>
-      <c r="B51" s="43">
-        <f>B50-B48</f>
-        <v/>
-      </c>
-      <c r="C51" s="46">
-        <f>IF(ROUND(B51,2)=0,"FULLY RECONCILED - nil hours variance","VARIANCE - investigate")</f>
-        <v/>
-      </c>
+      <c r="A51" s="38" t="inlineStr">
+        <is>
+          <t>Total paid hours matched to a timesheet line in Section C</t>
+        </is>
+      </c>
+      <c r="B51" s="41">
+        <f>J37</f>
+        <v/>
+      </c>
+      <c r="C51" s="45" t="inlineStr"/>
       <c r="D51" s="24" t="n"/>
       <c r="E51" s="24" t="n"/>
       <c r="F51" s="24" t="n"/>
@@ -2876,11 +3010,23 @@
       <c r="R51" s="24" t="n"/>
       <c r="S51" s="24" t="n"/>
       <c r="T51" s="24" t="n"/>
+      <c r="U51" s="24" t="n"/>
+      <c r="V51" s="24" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="24" t="n"/>
-      <c r="B52" s="24" t="n"/>
-      <c r="C52" s="24" t="n"/>
+      <c r="A52" s="38" t="inlineStr">
+        <is>
+          <t>Unmatched paid hours</t>
+        </is>
+      </c>
+      <c r="B52" s="41">
+        <f>B50-B51</f>
+        <v/>
+      </c>
+      <c r="C52" s="45">
+        <f>IF(ROUND(B52,2)=0,"OK - every paid hour ties to a timesheet line","INVESTIGATE - unmatched paid hours")</f>
+        <v/>
+      </c>
       <c r="D52" s="24" t="n"/>
       <c r="E52" s="24" t="n"/>
       <c r="F52" s="24" t="n"/>
@@ -2898,24 +3044,29 @@
       <c r="R52" s="24" t="n"/>
       <c r="S52" s="24" t="n"/>
       <c r="T52" s="24" t="n"/>
+      <c r="U52" s="24" t="n"/>
+      <c r="V52" s="24" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="36" t="inlineStr">
-        <is>
-          <t>F.  FINDINGS</t>
-        </is>
-      </c>
-      <c r="B53" s="36" t="n"/>
-      <c r="C53" s="36" t="n"/>
-      <c r="D53" s="36" t="n"/>
-      <c r="E53" s="36" t="n"/>
-      <c r="F53" s="36" t="n"/>
-      <c r="G53" s="36" t="n"/>
-      <c r="H53" s="36" t="n"/>
-      <c r="I53" s="36" t="n"/>
-      <c r="J53" s="36" t="n"/>
-      <c r="K53" s="36" t="n"/>
-      <c r="L53" s="36" t="n"/>
+      <c r="A53" s="38" t="inlineStr">
+        <is>
+          <t>Total timesheet hours per the screenshots</t>
+        </is>
+      </c>
+      <c r="B53" s="41">
+        <f>I37</f>
+        <v/>
+      </c>
+      <c r="C53" s="45" t="inlineStr"/>
+      <c r="D53" s="24" t="n"/>
+      <c r="E53" s="24" t="n"/>
+      <c r="F53" s="24" t="n"/>
+      <c r="G53" s="24" t="n"/>
+      <c r="H53" s="24" t="n"/>
+      <c r="I53" s="24" t="n"/>
+      <c r="J53" s="24" t="n"/>
+      <c r="K53" s="24" t="n"/>
+      <c r="L53" s="24" t="n"/>
       <c r="M53" s="24" t="n"/>
       <c r="N53" s="24" t="n"/>
       <c r="O53" s="24" t="n"/>
@@ -2924,18 +3075,28 @@
       <c r="R53" s="24" t="n"/>
       <c r="S53" s="24" t="n"/>
       <c r="T53" s="24" t="n"/>
+      <c r="U53" s="24" t="n"/>
+      <c r="V53" s="24" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="47" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B54" s="48" t="inlineStr">
-        <is>
-          <t>The 16 hours queried (24 Aug and 28 Aug, DTTL) are NOT missing - they were paid in full.</t>
-        </is>
-      </c>
+      <c r="A54" s="42" t="inlineStr">
+        <is>
+          <t>HOURS VARIANCE (timesheet less paid)</t>
+        </is>
+      </c>
+      <c r="B54" s="43">
+        <f>B53-B51</f>
+        <v/>
+      </c>
+      <c r="C54" s="54">
+        <f>IF(ROUND(B54,2)=0,"FULLY RECONCILED - nil hours variance","VARIANCE - investigate")</f>
+        <v/>
+      </c>
+      <c r="D54" s="24" t="n"/>
+      <c r="E54" s="24" t="n"/>
+      <c r="F54" s="24" t="n"/>
+      <c r="G54" s="24" t="n"/>
+      <c r="H54" s="24" t="n"/>
       <c r="I54" s="24" t="n"/>
       <c r="J54" s="24" t="n"/>
       <c r="K54" s="24" t="n"/>
@@ -2948,14 +3109,22 @@
       <c r="R54" s="24" t="n"/>
       <c r="S54" s="24" t="n"/>
       <c r="T54" s="24" t="n"/>
-    </row>
-    <row r="55" ht="34" customHeight="1" s="12">
+      <c r="U54" s="24" t="n"/>
+      <c r="V54" s="24" t="n"/>
+    </row>
+    <row r="55">
       <c r="A55" s="24" t="n"/>
-      <c r="B55" s="49" t="inlineStr">
-        <is>
-          <t>Both days were paid in the 20 Sep 2026 pay run: 24/08 as 3.5 hrs + 4.5 hrs, and 28/08 as 3.5 hrs + 4.5 hrs. 16 hours in total, nil shortfall. See Section A for the exact pay-run lines, and the two highlighted rows in Section C.</t>
-        </is>
-      </c>
+      <c r="B55" s="24" t="n"/>
+      <c r="C55" s="24" t="n"/>
+      <c r="D55" s="24" t="n"/>
+      <c r="E55" s="24" t="n"/>
+      <c r="F55" s="24" t="n"/>
+      <c r="G55" s="24" t="n"/>
+      <c r="H55" s="24" t="n"/>
+      <c r="I55" s="24" t="n"/>
+      <c r="J55" s="24" t="n"/>
+      <c r="K55" s="24" t="n"/>
+      <c r="L55" s="24" t="n"/>
       <c r="M55" s="24" t="n"/>
       <c r="N55" s="24" t="n"/>
       <c r="O55" s="24" t="n"/>
@@ -2964,20 +3133,26 @@
       <c r="R55" s="24" t="n"/>
       <c r="S55" s="24" t="n"/>
       <c r="T55" s="24" t="n"/>
+      <c r="U55" s="24" t="n"/>
+      <c r="V55" s="24" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="24" t="n"/>
-      <c r="B56" s="24" t="n"/>
-      <c r="C56" s="24" t="n"/>
-      <c r="D56" s="24" t="n"/>
-      <c r="E56" s="24" t="n"/>
-      <c r="F56" s="24" t="n"/>
-      <c r="G56" s="24" t="n"/>
-      <c r="H56" s="24" t="n"/>
-      <c r="I56" s="24" t="n"/>
-      <c r="J56" s="24" t="n"/>
-      <c r="K56" s="24" t="n"/>
-      <c r="L56" s="24" t="n"/>
+      <c r="A56" s="37" t="inlineStr">
+        <is>
+          <t>F.  FINDINGS</t>
+        </is>
+      </c>
+      <c r="B56" s="37" t="n"/>
+      <c r="C56" s="37" t="n"/>
+      <c r="D56" s="37" t="n"/>
+      <c r="E56" s="37" t="n"/>
+      <c r="F56" s="37" t="n"/>
+      <c r="G56" s="37" t="n"/>
+      <c r="H56" s="37" t="n"/>
+      <c r="I56" s="37" t="n"/>
+      <c r="J56" s="37" t="n"/>
+      <c r="K56" s="37" t="n"/>
+      <c r="L56" s="37" t="n"/>
       <c r="M56" s="24" t="n"/>
       <c r="N56" s="24" t="n"/>
       <c r="O56" s="24" t="n"/>
@@ -2986,16 +3161,18 @@
       <c r="R56" s="24" t="n"/>
       <c r="S56" s="24" t="n"/>
       <c r="T56" s="24" t="n"/>
+      <c r="U56" s="24" t="n"/>
+      <c r="V56" s="24" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="47" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B57" s="48" t="inlineStr">
-        <is>
-          <t>Hours reconcile in full across all four fortnights.</t>
+      <c r="A57" s="55" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B57" s="56" t="inlineStr">
+        <is>
+          <t>The 16 hours queried (24 Aug and 28 Aug, DTTL) are NOT missing - they were paid in full.</t>
         </is>
       </c>
       <c r="I57" s="24" t="n"/>
@@ -3010,12 +3187,14 @@
       <c r="R57" s="24" t="n"/>
       <c r="S57" s="24" t="n"/>
       <c r="T57" s="24" t="n"/>
-    </row>
-    <row r="58" ht="34" customHeight="1" s="12">
+      <c r="U57" s="24" t="n"/>
+      <c r="V57" s="24" t="n"/>
+    </row>
+    <row r="58" ht="36" customHeight="1" s="12">
       <c r="A58" s="24" t="n"/>
-      <c r="B58" s="49" t="inlineStr">
-        <is>
-          <t>All 111.50 timesheet hours have been paid. Nil variance at day level, at fortnight level and in total, and every paid line ties back to a timesheet entry.</t>
+      <c r="B58" s="57" t="inlineStr">
+        <is>
+          <t>Both days fall in the pay period 22/08/2026 - 04/09/2026, which was paid on 08/09/2026. Each was paid as 3.5 hrs + 4.5 hrs either side of the unpaid break, which is why neither shows as a single 8 hour entry. 16 hours in total, nil shortfall. See Section A and the two highlighted rows in Section C.</t>
         </is>
       </c>
       <c r="M58" s="24" t="n"/>
@@ -3026,6 +3205,8 @@
       <c r="R58" s="24" t="n"/>
       <c r="S58" s="24" t="n"/>
       <c r="T58" s="24" t="n"/>
+      <c r="U58" s="24" t="n"/>
+      <c r="V58" s="24" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="24" t="n"/>
@@ -3048,16 +3229,18 @@
       <c r="R59" s="24" t="n"/>
       <c r="S59" s="24" t="n"/>
       <c r="T59" s="24" t="n"/>
+      <c r="U59" s="24" t="n"/>
+      <c r="V59" s="24" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="47" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B60" s="48" t="inlineStr">
-        <is>
-          <t>Fortnight ending 04/09/2026 was paid across two pay runs - the likely cause of the query.</t>
+      <c r="A60" s="55" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B60" s="56" t="inlineStr">
+        <is>
+          <t>Hours reconcile in full across all four pay periods.</t>
         </is>
       </c>
       <c r="I60" s="24" t="n"/>
@@ -3072,12 +3255,14 @@
       <c r="R60" s="24" t="n"/>
       <c r="S60" s="24" t="n"/>
       <c r="T60" s="24" t="n"/>
-    </row>
-    <row r="61" ht="34" customHeight="1" s="12">
+      <c r="U60" s="24" t="n"/>
+      <c r="V60" s="24" t="n"/>
+    </row>
+    <row r="61" ht="36" customHeight="1" s="12">
       <c r="A61" s="24" t="n"/>
-      <c r="B61" s="49" t="inlineStr">
-        <is>
-          <t>48 hrs of DTTL work (including the two days queried) went through the 20 Sep 2026 run, and 23.50 hrs of PwC National Pool work went through the 22 Sep 2026 run. Total 71.50 hrs, which agrees to the timesheet. Anyone checking a single payslip for that fortnight would only see part of it.</t>
+      <c r="B61" s="57" t="inlineStr">
+        <is>
+          <t>All 111.50 timesheet hours have been paid. Nil variance at day level, at pay period level and in total, and every paid line ties back to a timesheet entry.</t>
         </is>
       </c>
       <c r="M61" s="24" t="n"/>
@@ -3088,6 +3273,8 @@
       <c r="R61" s="24" t="n"/>
       <c r="S61" s="24" t="n"/>
       <c r="T61" s="24" t="n"/>
+      <c r="U61" s="24" t="n"/>
+      <c r="V61" s="24" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="24" t="n"/>
@@ -3110,16 +3297,18 @@
       <c r="R62" s="24" t="n"/>
       <c r="S62" s="24" t="n"/>
       <c r="T62" s="24" t="n"/>
+      <c r="U62" s="24" t="n"/>
+      <c r="V62" s="24" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="47" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B63" s="48" t="inlineStr">
-        <is>
-          <t>Two adjustment lines on the 21 Aug 2026 run net to nil hours.</t>
+      <c r="A63" s="55" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B63" s="56" t="inlineStr">
+        <is>
+          <t>CHECK THIS - 23.50 hours may have been paid two weeks late.</t>
         </is>
       </c>
       <c r="I63" s="24" t="n"/>
@@ -3134,12 +3323,14 @@
       <c r="R63" s="24" t="n"/>
       <c r="S63" s="24" t="n"/>
       <c r="T63" s="24" t="n"/>
-    </row>
-    <row r="64" ht="34" customHeight="1" s="12">
+      <c r="U63" s="24" t="n"/>
+      <c r="V63" s="24" t="n"/>
+    </row>
+    <row r="64" ht="36" customHeight="1" s="12">
       <c r="A64" s="24" t="n"/>
-      <c r="B64" s="49" t="inlineStr">
-        <is>
-          <t>A reversal of 16 hrs and a re-payment of 16 hrs appear on that run. They were raised to correct the pay rate used for the fortnight ending 07/08/2026, not to change hours. No hours were added or removed, so they do not affect this reconciliation. See Section D.</t>
+      <c r="B64" s="57" t="inlineStr">
+        <is>
+          <t>The hours worked on 25, 26 and 27 August fall in the pay period 22/08/2026 - 04/09/2026, which was paid on 08/09/2026. In this workbook they sit on the 22 Sep 2026 tab, apart from the rest of that period. If that tab represents the run paid on 22/09/2026, those 23.50 hours were paid a fortnight after the rest of the period. The hours themselves are correct and fully paid - only the date they reached him is in question. Confirm against the payslips. These rows are shaded in Section C.</t>
         </is>
       </c>
       <c r="M64" s="24" t="n"/>
@@ -3150,6 +3341,8 @@
       <c r="R64" s="24" t="n"/>
       <c r="S64" s="24" t="n"/>
       <c r="T64" s="24" t="n"/>
+      <c r="U64" s="24" t="n"/>
+      <c r="V64" s="24" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="24" t="n"/>
@@ -3172,16 +3365,18 @@
       <c r="R65" s="24" t="n"/>
       <c r="S65" s="24" t="n"/>
       <c r="T65" s="24" t="n"/>
+      <c r="U65" s="24" t="n"/>
+      <c r="V65" s="24" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="47" t="inlineStr">
-        <is>
-          <t>5.</t>
-        </is>
-      </c>
-      <c r="B66" s="48" t="inlineStr">
-        <is>
-          <t>Those adjustment lines were booked to the wrong location.</t>
+      <c r="A66" s="55" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B66" s="56" t="inlineStr">
+        <is>
+          <t>The rate on the period 25/07/2026 - 07/08/2026 was wrong, and has been corrected.</t>
         </is>
       </c>
       <c r="I66" s="24" t="n"/>
@@ -3196,12 +3391,14 @@
       <c r="R66" s="24" t="n"/>
       <c r="S66" s="24" t="n"/>
       <c r="T66" s="24" t="n"/>
-    </row>
-    <row r="67" ht="34" customHeight="1" s="12">
+      <c r="U66" s="24" t="n"/>
+      <c r="V66" s="24" t="n"/>
+    </row>
+    <row r="67" ht="36" customHeight="1" s="12">
       <c r="A67" s="24" t="n"/>
-      <c r="B67" s="49" t="inlineStr">
-        <is>
-          <t>The original 16 hrs were split CBA 8 hrs, PwC - MEL Technician 4 hrs and Aware Super 4 hrs. The reversal and re-payment put all 16 hrs against CBA FT Tech MEL. Hours paid are correct, but job costing for PwC and Aware Super is understated by 4 hrs each and CBA is overstated by 8 hrs. Worth raising with payroll if client recharges run off this data.</t>
+      <c r="B67" s="57" t="inlineStr">
+        <is>
+          <t>16 hrs were first paid at $35.15/hr instead of $37.50/hr on 11/08/2026. Those hours were reversed and re-paid at $37.50/hr on 25/08/2026, so all hours now stand at the correct rate. Every other line across the four periods was paid at $37.50/hr.</t>
         </is>
       </c>
       <c r="M67" s="24" t="n"/>
@@ -3212,6 +3409,8 @@
       <c r="R67" s="24" t="n"/>
       <c r="S67" s="24" t="n"/>
       <c r="T67" s="24" t="n"/>
+      <c r="U67" s="24" t="n"/>
+      <c r="V67" s="24" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="24" t="n"/>
@@ -3234,16 +3433,18 @@
       <c r="R68" s="24" t="n"/>
       <c r="S68" s="24" t="n"/>
       <c r="T68" s="24" t="n"/>
+      <c r="U68" s="24" t="n"/>
+      <c r="V68" s="24" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="47" t="inlineStr">
-        <is>
-          <t>6.</t>
-        </is>
-      </c>
-      <c r="B69" s="48" t="inlineStr">
-        <is>
-          <t>Payment lag worth checking.</t>
+      <c r="A69" s="55" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B69" s="56" t="inlineStr">
+        <is>
+          <t>The rate-correction lines were booked to the wrong location.</t>
         </is>
       </c>
       <c r="I69" s="24" t="n"/>
@@ -3258,12 +3459,14 @@
       <c r="R69" s="24" t="n"/>
       <c r="S69" s="24" t="n"/>
       <c r="T69" s="24" t="n"/>
-    </row>
-    <row r="70" ht="34" customHeight="1" s="12">
+      <c r="U69" s="24" t="n"/>
+      <c r="V69" s="24" t="n"/>
+    </row>
+    <row r="70" ht="36" customHeight="1" s="12">
       <c r="A70" s="24" t="n"/>
-      <c r="B70" s="49" t="inlineStr">
-        <is>
-          <t>Work from 25-27 Aug was not paid until the 22 Sep 2026 run, roughly four weeks after it was worked. Check this against the payroll calendar if it was not expected.</t>
+      <c r="B70" s="57" t="inlineStr">
+        <is>
+          <t>The original 16 hrs were split CBA 8 hrs, PwC - MEL Technician 4 hrs and Aware Super 4 hrs. The reversal and re-payment put all 16 hrs against CBA FT Tech MEL. Hours and rate paid are correct, but job costing for PwC and Aware Super is understated by 4 hrs each and CBA is overstated by 8 hrs. Worth raising with payroll if client recharges run off this data.</t>
         </is>
       </c>
       <c r="M70" s="24" t="n"/>
@@ -3274,6 +3477,8 @@
       <c r="R70" s="24" t="n"/>
       <c r="S70" s="24" t="n"/>
       <c r="T70" s="24" t="n"/>
+      <c r="U70" s="24" t="n"/>
+      <c r="V70" s="24" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="24" t="n"/>
@@ -3296,16 +3501,20 @@
       <c r="R71" s="24" t="n"/>
       <c r="S71" s="24" t="n"/>
       <c r="T71" s="24" t="n"/>
+      <c r="U71" s="24" t="n"/>
+      <c r="V71" s="24" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="24" t="n"/>
-      <c r="B72" s="24" t="n"/>
-      <c r="C72" s="24" t="n"/>
-      <c r="D72" s="24" t="n"/>
-      <c r="E72" s="24" t="n"/>
-      <c r="F72" s="24" t="n"/>
-      <c r="G72" s="24" t="n"/>
-      <c r="H72" s="24" t="n"/>
+      <c r="A72" s="55" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B72" s="56" t="inlineStr">
+        <is>
+          <t>The pay period 08/08/2026 - 21/08/2026 carries three separate payment dates.</t>
+        </is>
+      </c>
       <c r="I72" s="24" t="n"/>
       <c r="J72" s="24" t="n"/>
       <c r="K72" s="24" t="n"/>
@@ -3318,11 +3527,14 @@
       <c r="R72" s="24" t="n"/>
       <c r="S72" s="24" t="n"/>
       <c r="T72" s="24" t="n"/>
-    </row>
-    <row r="73" ht="44" customHeight="1" s="12">
-      <c r="A73" s="25" t="inlineStr">
-        <is>
-          <t>Source of timesheet data: the timesheet screenshots for the fortnights ending 07/08/2026, 21/08/2026, 04/09/2026 and 18/09/2026, all showing status PROCESSED. Source of paid data: the Earnings Details tabs in this workbook, with the rate, gross earnings, taxable earnings and superannuation columns removed. Paid figures are live formulas - if a pay-run tab is updated, this reconciliation updates with it. Columns M and N were added to each pay-run tab: M pulls the work date out of the Notes text, N confirms the line was matched here.</t>
+      <c r="U72" s="24" t="n"/>
+      <c r="V72" s="24" t="n"/>
+    </row>
+    <row r="73" ht="36" customHeight="1" s="12">
+      <c r="A73" s="24" t="n"/>
+      <c r="B73" s="57" t="inlineStr">
+        <is>
+          <t>The pay history shows that period paid on 25/08/2026, 26/08/2026 and 28/08/2026. This reconciliation uses 25/08/2026, the first of them. The extra runs are consistent with the rate correction being processed separately. Worth confirming what the 26/08 and 28/08 runs covered.</t>
         </is>
       </c>
       <c r="M73" s="24" t="n"/>
@@ -3333,6 +3545,8 @@
       <c r="R73" s="24" t="n"/>
       <c r="S73" s="24" t="n"/>
       <c r="T73" s="24" t="n"/>
+      <c r="U73" s="24" t="n"/>
+      <c r="V73" s="24" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="24" t="n"/>
@@ -3355,6 +3569,8 @@
       <c r="R74" s="24" t="n"/>
       <c r="S74" s="24" t="n"/>
       <c r="T74" s="24" t="n"/>
+      <c r="U74" s="24" t="n"/>
+      <c r="V74" s="24" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="24" t="n"/>
@@ -3377,20 +3593,15 @@
       <c r="R75" s="24" t="n"/>
       <c r="S75" s="24" t="n"/>
       <c r="T75" s="24" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="24" t="n"/>
-      <c r="B76" s="24" t="n"/>
-      <c r="C76" s="24" t="n"/>
-      <c r="D76" s="24" t="n"/>
-      <c r="E76" s="24" t="n"/>
-      <c r="F76" s="24" t="n"/>
-      <c r="G76" s="24" t="n"/>
-      <c r="H76" s="24" t="n"/>
-      <c r="I76" s="24" t="n"/>
-      <c r="J76" s="24" t="n"/>
-      <c r="K76" s="24" t="n"/>
-      <c r="L76" s="24" t="n"/>
+      <c r="U75" s="24" t="n"/>
+      <c r="V75" s="24" t="n"/>
+    </row>
+    <row r="76" ht="40" customHeight="1" s="12">
+      <c r="A76" s="25" t="inlineStr">
+        <is>
+          <t>Timesheet hours transcribed from the timesheet screenshots for the periods ending 07/08/2026, 21/08/2026, 04/09/2026 and 18/09/2026, all showing status PROCESSED. Paid hours from the Earnings Details tabs in this workbook. Pay periods and dates paid taken from the Employment Hero pay history. NOTE: the tab names in this workbook are NOT payment dates - the Pay Period and Date Paid columns are the authoritative reference.</t>
+        </is>
+      </c>
       <c r="M76" s="24" t="n"/>
       <c r="N76" s="24" t="n"/>
       <c r="O76" s="24" t="n"/>
@@ -3399,6 +3610,8 @@
       <c r="R76" s="24" t="n"/>
       <c r="S76" s="24" t="n"/>
       <c r="T76" s="24" t="n"/>
+      <c r="U76" s="24" t="n"/>
+      <c r="V76" s="24" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="24" t="n"/>
@@ -3421,6 +3634,8 @@
       <c r="R77" s="24" t="n"/>
       <c r="S77" s="24" t="n"/>
       <c r="T77" s="24" t="n"/>
+      <c r="U77" s="24" t="n"/>
+      <c r="V77" s="24" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="24" t="n"/>
@@ -3443,6 +3658,8 @@
       <c r="R78" s="24" t="n"/>
       <c r="S78" s="24" t="n"/>
       <c r="T78" s="24" t="n"/>
+      <c r="U78" s="24" t="n"/>
+      <c r="V78" s="24" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="24" t="n"/>
@@ -3465,6 +3682,8 @@
       <c r="R79" s="24" t="n"/>
       <c r="S79" s="24" t="n"/>
       <c r="T79" s="24" t="n"/>
+      <c r="U79" s="24" t="n"/>
+      <c r="V79" s="24" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="24" t="n"/>
@@ -3487,6 +3706,8 @@
       <c r="R80" s="24" t="n"/>
       <c r="S80" s="24" t="n"/>
       <c r="T80" s="24" t="n"/>
+      <c r="U80" s="24" t="n"/>
+      <c r="V80" s="24" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="24" t="n"/>
@@ -3509,6 +3730,8 @@
       <c r="R81" s="24" t="n"/>
       <c r="S81" s="24" t="n"/>
       <c r="T81" s="24" t="n"/>
+      <c r="U81" s="24" t="n"/>
+      <c r="V81" s="24" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="24" t="n"/>
@@ -3531,6 +3754,8 @@
       <c r="R82" s="24" t="n"/>
       <c r="S82" s="24" t="n"/>
       <c r="T82" s="24" t="n"/>
+      <c r="U82" s="24" t="n"/>
+      <c r="V82" s="24" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="24" t="n"/>
@@ -3553,6 +3778,8 @@
       <c r="R83" s="24" t="n"/>
       <c r="S83" s="24" t="n"/>
       <c r="T83" s="24" t="n"/>
+      <c r="U83" s="24" t="n"/>
+      <c r="V83" s="24" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="24" t="n"/>
@@ -3575,6 +3802,8 @@
       <c r="R84" s="24" t="n"/>
       <c r="S84" s="24" t="n"/>
       <c r="T84" s="24" t="n"/>
+      <c r="U84" s="24" t="n"/>
+      <c r="V84" s="24" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="24" t="n"/>
@@ -3597,6 +3826,8 @@
       <c r="R85" s="24" t="n"/>
       <c r="S85" s="24" t="n"/>
       <c r="T85" s="24" t="n"/>
+      <c r="U85" s="24" t="n"/>
+      <c r="V85" s="24" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="24" t="n"/>
@@ -3619,6 +3850,8 @@
       <c r="R86" s="24" t="n"/>
       <c r="S86" s="24" t="n"/>
       <c r="T86" s="24" t="n"/>
+      <c r="U86" s="24" t="n"/>
+      <c r="V86" s="24" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="24" t="n"/>
@@ -3641,6 +3874,8 @@
       <c r="R87" s="24" t="n"/>
       <c r="S87" s="24" t="n"/>
       <c r="T87" s="24" t="n"/>
+      <c r="U87" s="24" t="n"/>
+      <c r="V87" s="24" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="24" t="n"/>
@@ -3663,6 +3898,8 @@
       <c r="R88" s="24" t="n"/>
       <c r="S88" s="24" t="n"/>
       <c r="T88" s="24" t="n"/>
+      <c r="U88" s="24" t="n"/>
+      <c r="V88" s="24" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="24" t="n"/>
@@ -3685,6 +3922,8 @@
       <c r="R89" s="24" t="n"/>
       <c r="S89" s="24" t="n"/>
       <c r="T89" s="24" t="n"/>
+      <c r="U89" s="24" t="n"/>
+      <c r="V89" s="24" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="24" t="n"/>
@@ -3707,67 +3946,184 @@
       <c r="R90" s="24" t="n"/>
       <c r="S90" s="24" t="n"/>
       <c r="T90" s="24" t="n"/>
+      <c r="U90" s="24" t="n"/>
+      <c r="V90" s="24" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="24" t="n"/>
+      <c r="B91" s="24" t="n"/>
+      <c r="C91" s="24" t="n"/>
+      <c r="D91" s="24" t="n"/>
+      <c r="E91" s="24" t="n"/>
+      <c r="F91" s="24" t="n"/>
+      <c r="G91" s="24" t="n"/>
+      <c r="H91" s="24" t="n"/>
+      <c r="I91" s="24" t="n"/>
+      <c r="J91" s="24" t="n"/>
+      <c r="K91" s="24" t="n"/>
+      <c r="L91" s="24" t="n"/>
+      <c r="M91" s="24" t="n"/>
+      <c r="N91" s="24" t="n"/>
+      <c r="O91" s="24" t="n"/>
+      <c r="P91" s="24" t="n"/>
+      <c r="Q91" s="24" t="n"/>
+      <c r="R91" s="24" t="n"/>
+      <c r="S91" s="24" t="n"/>
+      <c r="T91" s="24" t="n"/>
+      <c r="U91" s="24" t="n"/>
+      <c r="V91" s="24" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="24" t="n"/>
+      <c r="B92" s="24" t="n"/>
+      <c r="C92" s="24" t="n"/>
+      <c r="D92" s="24" t="n"/>
+      <c r="E92" s="24" t="n"/>
+      <c r="F92" s="24" t="n"/>
+      <c r="G92" s="24" t="n"/>
+      <c r="H92" s="24" t="n"/>
+      <c r="I92" s="24" t="n"/>
+      <c r="J92" s="24" t="n"/>
+      <c r="K92" s="24" t="n"/>
+      <c r="L92" s="24" t="n"/>
+      <c r="M92" s="24" t="n"/>
+      <c r="N92" s="24" t="n"/>
+      <c r="O92" s="24" t="n"/>
+      <c r="P92" s="24" t="n"/>
+      <c r="Q92" s="24" t="n"/>
+      <c r="R92" s="24" t="n"/>
+      <c r="S92" s="24" t="n"/>
+      <c r="T92" s="24" t="n"/>
+      <c r="U92" s="24" t="n"/>
+      <c r="V92" s="24" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="24" t="n"/>
+      <c r="B93" s="24" t="n"/>
+      <c r="C93" s="24" t="n"/>
+      <c r="D93" s="24" t="n"/>
+      <c r="E93" s="24" t="n"/>
+      <c r="F93" s="24" t="n"/>
+      <c r="G93" s="24" t="n"/>
+      <c r="H93" s="24" t="n"/>
+      <c r="I93" s="24" t="n"/>
+      <c r="J93" s="24" t="n"/>
+      <c r="K93" s="24" t="n"/>
+      <c r="L93" s="24" t="n"/>
+      <c r="M93" s="24" t="n"/>
+      <c r="N93" s="24" t="n"/>
+      <c r="O93" s="24" t="n"/>
+      <c r="P93" s="24" t="n"/>
+      <c r="Q93" s="24" t="n"/>
+      <c r="R93" s="24" t="n"/>
+      <c r="S93" s="24" t="n"/>
+      <c r="T93" s="24" t="n"/>
+      <c r="U93" s="24" t="n"/>
+      <c r="V93" s="24" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="24" t="n"/>
+      <c r="B94" s="24" t="n"/>
+      <c r="C94" s="24" t="n"/>
+      <c r="D94" s="24" t="n"/>
+      <c r="E94" s="24" t="n"/>
+      <c r="F94" s="24" t="n"/>
+      <c r="G94" s="24" t="n"/>
+      <c r="H94" s="24" t="n"/>
+      <c r="I94" s="24" t="n"/>
+      <c r="J94" s="24" t="n"/>
+      <c r="K94" s="24" t="n"/>
+      <c r="L94" s="24" t="n"/>
+      <c r="M94" s="24" t="n"/>
+      <c r="N94" s="24" t="n"/>
+      <c r="O94" s="24" t="n"/>
+      <c r="P94" s="24" t="n"/>
+      <c r="Q94" s="24" t="n"/>
+      <c r="R94" s="24" t="n"/>
+      <c r="S94" s="24" t="n"/>
+      <c r="T94" s="24" t="n"/>
+      <c r="U94" s="24" t="n"/>
+      <c r="V94" s="24" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="24" t="n"/>
+      <c r="B95" s="24" t="n"/>
+      <c r="C95" s="24" t="n"/>
+      <c r="D95" s="24" t="n"/>
+      <c r="E95" s="24" t="n"/>
+      <c r="F95" s="24" t="n"/>
+      <c r="G95" s="24" t="n"/>
+      <c r="H95" s="24" t="n"/>
+      <c r="I95" s="24" t="n"/>
+      <c r="J95" s="24" t="n"/>
+      <c r="K95" s="24" t="n"/>
+      <c r="L95" s="24" t="n"/>
+      <c r="M95" s="24" t="n"/>
+      <c r="N95" s="24" t="n"/>
+      <c r="O95" s="24" t="n"/>
+      <c r="P95" s="24" t="n"/>
+      <c r="Q95" s="24" t="n"/>
+      <c r="R95" s="24" t="n"/>
+      <c r="S95" s="24" t="n"/>
+      <c r="T95" s="24" t="n"/>
+      <c r="U95" s="24" t="n"/>
+      <c r="V95" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A73:L73"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B66:H66"/>
     <mergeCell ref="B58:L58"/>
+    <mergeCell ref="B73:L73"/>
     <mergeCell ref="B70:L70"/>
     <mergeCell ref="B57:H57"/>
+    <mergeCell ref="A76:L76"/>
     <mergeCell ref="B64:L64"/>
-    <mergeCell ref="B55:L55"/>
     <mergeCell ref="B69:H69"/>
-    <mergeCell ref="B54:H54"/>
     <mergeCell ref="A9:L9"/>
+    <mergeCell ref="B72:H72"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B60:H60"/>
     <mergeCell ref="B61:L61"/>
     <mergeCell ref="B63:H63"/>
   </mergeCells>
-  <conditionalFormatting sqref="E13:E17">
+  <conditionalFormatting sqref="G13:G17">
     <cfRule type="cellIs" priority="1" operator="notEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J21:J37">
+  <conditionalFormatting sqref="K21:K37">
     <cfRule type="cellIs" priority="2" operator="notEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:F8">
+  <conditionalFormatting sqref="H6:H8">
     <cfRule type="cellIs" priority="3" operator="notEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13:F17">
+  <conditionalFormatting sqref="H13:H17">
     <cfRule type="expression" priority="4" dxfId="1">
-      <formula>ISNUMBER(SEARCH("Reconciled",F13))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("Reconciled",H13))+ISNUMBER(SEARCH("FULLY",H13))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="0">
-      <formula>ISNUMBER(SEARCH("VARIANCE",F13))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("VARIANCE",H13))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K37">
+  <conditionalFormatting sqref="C50:C54">
     <cfRule type="expression" priority="6" dxfId="1">
-      <formula>ISNUMBER(SEARCH("AGREE",K37))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("OK",C50))+ISNUMBER(SEARCH("FULLY",C50))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="0">
+      <formula>ISNUMBER(SEARCH("INVESTIGATE",C50))+ISNUMBER(SEARCH("VARIANCE",C50))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C47:C51">
-    <cfRule type="expression" priority="7" dxfId="1">
-      <formula>ISNUMBER(SEARCH("OK",C47))+ISNUMBER(SEARCH("FULLY",C47))&gt;0</formula>
+  <conditionalFormatting sqref="J6:J8">
+    <cfRule type="expression" priority="8" dxfId="1">
+      <formula>ISNUMBER(SEARCH("PAID IN FULL",J6))+ISNUMBER(SEARCH("NIL OWING",J6))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="0">
-      <formula>ISNUMBER(SEARCH("INVESTIGATE",C47))+ISNUMBER(SEARCH("VARIANCE",C47))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I6:I8">
-    <cfRule type="expression" priority="9" dxfId="1">
-      <formula>ISNUMBER(SEARCH("PAID IN FULL",I6))+ISNUMBER(SEARCH("NIL OWING",I6))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="10" dxfId="0">
-      <formula>ISNUMBER(SEARCH("SHORTFALL",I6))+ISNUMBER(SEARCH("OWING - ",I6))&gt;0</formula>
+    <cfRule type="expression" priority="9" dxfId="0">
+      <formula>ISNUMBER(SEARCH("SHORTFALL",J6))+ISNUMBER(SEARCH("OWING - ",J6))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3872,12 +4228,12 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="M2" s="50" t="inlineStr">
+      <c r="M2" s="58" t="inlineStr">
         <is>
           <t>Work Date (helper)</t>
         </is>
       </c>
-      <c r="N2" s="50" t="inlineStr">
+      <c r="N2" s="58" t="inlineStr">
         <is>
           <t>Matched to Timesheet?</t>
         </is>
@@ -3931,12 +4287,12 @@
           <t>25/08/2026 - 08:00 to 12:00</t>
         </is>
       </c>
-      <c r="M3" s="51">
+      <c r="M3" s="59">
         <f>IFERROR(DATE(VALUE(MID(L3,FIND("/",L3,FIND("/",L3)+1)+1,4)),VALUE(MID(L3,FIND("/",L3)+1,FIND("/",L3,FIND("/",L3)+1)-FIND("/",L3)-1)),VALUE(LEFT(L3,FIND("/",L3)-1))),IF(ISNUMBER(L3),L3,""))</f>
         <v/>
       </c>
       <c r="N3">
-        <f>IF(M3="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M3,'Summary '!$D$21:$D$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M3="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M3,'Summary '!$E$21:$E$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -3988,12 +4344,12 @@
           <t>25/08/2026 - 13:00 to 17:00</t>
         </is>
       </c>
-      <c r="M4" s="51">
+      <c r="M4" s="59">
         <f>IFERROR(DATE(VALUE(MID(L4,FIND("/",L4,FIND("/",L4)+1)+1,4)),VALUE(MID(L4,FIND("/",L4)+1,FIND("/",L4,FIND("/",L4)+1)-FIND("/",L4)-1)),VALUE(LEFT(L4,FIND("/",L4)-1))),IF(ISNUMBER(L4),L4,""))</f>
         <v/>
       </c>
       <c r="N4">
-        <f>IF(M4="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M4,'Summary '!$D$21:$D$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M4="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M4,'Summary '!$E$21:$E$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4045,12 +4401,12 @@
           <t>26/08/2026 - 08:00 to 12:00</t>
         </is>
       </c>
-      <c r="M5" s="51">
+      <c r="M5" s="59">
         <f>IFERROR(DATE(VALUE(MID(L5,FIND("/",L5,FIND("/",L5)+1)+1,4)),VALUE(MID(L5,FIND("/",L5)+1,FIND("/",L5,FIND("/",L5)+1)-FIND("/",L5)-1)),VALUE(LEFT(L5,FIND("/",L5)-1))),IF(ISNUMBER(L5),L5,""))</f>
         <v/>
       </c>
       <c r="N5">
-        <f>IF(M5="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M5,'Summary '!$D$21:$D$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M5="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M5,'Summary '!$E$21:$E$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4102,12 +4458,12 @@
           <t>26/08/2026 - 12:30 to 16:00</t>
         </is>
       </c>
-      <c r="M6" s="51">
+      <c r="M6" s="59">
         <f>IFERROR(DATE(VALUE(MID(L6,FIND("/",L6,FIND("/",L6)+1)+1,4)),VALUE(MID(L6,FIND("/",L6)+1,FIND("/",L6,FIND("/",L6)+1)-FIND("/",L6)-1)),VALUE(LEFT(L6,FIND("/",L6)-1))),IF(ISNUMBER(L6),L6,""))</f>
         <v/>
       </c>
       <c r="N6">
-        <f>IF(M6="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M6,'Summary '!$D$21:$D$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M6="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M6,'Summary '!$E$21:$E$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4159,12 +4515,12 @@
           <t>27/08/2026 - 08:00 to 12:00</t>
         </is>
       </c>
-      <c r="M7" s="51">
+      <c r="M7" s="59">
         <f>IFERROR(DATE(VALUE(MID(L7,FIND("/",L7,FIND("/",L7)+1)+1,4)),VALUE(MID(L7,FIND("/",L7)+1,FIND("/",L7,FIND("/",L7)+1)-FIND("/",L7)-1)),VALUE(LEFT(L7,FIND("/",L7)-1))),IF(ISNUMBER(L7),L7,""))</f>
         <v/>
       </c>
       <c r="N7">
-        <f>IF(M7="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M7,'Summary '!$D$21:$D$36,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M7="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M7,'Summary '!$E$21:$E$36,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4216,12 +4572,12 @@
           <t>27/08/2026 - 13:00 to 17:00</t>
         </is>
       </c>
-      <c r="M8" s="51">
+      <c r="M8" s="59">
         <f>IFERROR(DATE(VALUE(MID(L8,FIND("/",L8,FIND("/",L8)+1)+1,4)),VALUE(MID(L8,FIND("/",L8)+1,FIND("/",L8,FIND("/",L8)+1)-FIND("/",L8)-1)),VALUE(LEFT(L8,FIND("/",L8)-1))),IF(ISNUMBER(L8),L8,""))</f>
         <v/>
       </c>
       <c r="N8">
-        <f>IF(M8="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M8,'Summary '!$D$21:$D$36,K8)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M8="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M8,'Summary '!$E$21:$E$36,K8)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4273,12 +4629,12 @@
           <t>10/09/2026 - 08:00 to 12:00</t>
         </is>
       </c>
-      <c r="M9" s="51">
+      <c r="M9" s="59">
         <f>IFERROR(DATE(VALUE(MID(L9,FIND("/",L9,FIND("/",L9)+1)+1,4)),VALUE(MID(L9,FIND("/",L9)+1,FIND("/",L9,FIND("/",L9)+1)-FIND("/",L9)-1)),VALUE(LEFT(L9,FIND("/",L9)-1))),IF(ISNUMBER(L9),L9,""))</f>
         <v/>
       </c>
       <c r="N9">
-        <f>IF(M9="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M9,'Summary '!$D$21:$D$36,K9)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M9="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M9,'Summary '!$E$21:$E$36,K9)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4330,12 +4686,12 @@
           <t>10/09/2026 - 13:00 to 17:00</t>
         </is>
       </c>
-      <c r="M10" s="51">
+      <c r="M10" s="59">
         <f>IFERROR(DATE(VALUE(MID(L10,FIND("/",L10,FIND("/",L10)+1)+1,4)),VALUE(MID(L10,FIND("/",L10)+1,FIND("/",L10,FIND("/",L10)+1)-FIND("/",L10)-1)),VALUE(LEFT(L10,FIND("/",L10)-1))),IF(ISNUMBER(L10),L10,""))</f>
         <v/>
       </c>
       <c r="N10">
-        <f>IF(M10="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M10,'Summary '!$D$21:$D$36,K10)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M10="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M10,'Summary '!$E$21:$E$36,K10)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4387,12 +4743,12 @@
           <t>17/09/2026 - 11:30 to 15:30</t>
         </is>
       </c>
-      <c r="M11" s="51">
+      <c r="M11" s="59">
         <f>IFERROR(DATE(VALUE(MID(L11,FIND("/",L11,FIND("/",L11)+1)+1,4)),VALUE(MID(L11,FIND("/",L11)+1,FIND("/",L11,FIND("/",L11)+1)-FIND("/",L11)-1)),VALUE(LEFT(L11,FIND("/",L11)-1))),IF(ISNUMBER(L11),L11,""))</f>
         <v/>
       </c>
       <c r="N11">
-        <f>IF(M11="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M11,'Summary '!$D$21:$D$36,K11)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M11="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M11,'Summary '!$E$21:$E$36,K11)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4500,12 +4856,12 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="M2" s="50" t="inlineStr">
+      <c r="M2" s="58" t="inlineStr">
         <is>
           <t>Work Date (helper)</t>
         </is>
       </c>
-      <c r="N2" s="50" t="inlineStr">
+      <c r="N2" s="58" t="inlineStr">
         <is>
           <t>Matched to Timesheet?</t>
         </is>
@@ -4559,12 +4915,12 @@
           <t>24/08/2026 - 08:30 to 12:00</t>
         </is>
       </c>
-      <c r="M3" s="51">
+      <c r="M3" s="59">
         <f>IFERROR(DATE(VALUE(MID(L3,FIND("/",L3,FIND("/",L3)+1)+1,4)),VALUE(MID(L3,FIND("/",L3)+1,FIND("/",L3,FIND("/",L3)+1)-FIND("/",L3)-1)),VALUE(LEFT(L3,FIND("/",L3)-1))),IF(ISNUMBER(L3),L3,""))</f>
         <v/>
       </c>
       <c r="N3">
-        <f>IF(M3="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M3,'Summary '!$D$21:$D$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M3="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M3,'Summary '!$E$21:$E$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4616,12 +4972,12 @@
           <t>24/08/2026 - 12:30 to 17:00</t>
         </is>
       </c>
-      <c r="M4" s="51">
+      <c r="M4" s="59">
         <f>IFERROR(DATE(VALUE(MID(L4,FIND("/",L4,FIND("/",L4)+1)+1,4)),VALUE(MID(L4,FIND("/",L4)+1,FIND("/",L4,FIND("/",L4)+1)-FIND("/",L4)-1)),VALUE(LEFT(L4,FIND("/",L4)-1))),IF(ISNUMBER(L4),L4,""))</f>
         <v/>
       </c>
       <c r="N4">
-        <f>IF(M4="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M4,'Summary '!$D$21:$D$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M4="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M4,'Summary '!$E$21:$E$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4673,12 +5029,12 @@
           <t>28/08/2026 - 08:30 to 12:00</t>
         </is>
       </c>
-      <c r="M5" s="51">
+      <c r="M5" s="59">
         <f>IFERROR(DATE(VALUE(MID(L5,FIND("/",L5,FIND("/",L5)+1)+1,4)),VALUE(MID(L5,FIND("/",L5)+1,FIND("/",L5,FIND("/",L5)+1)-FIND("/",L5)-1)),VALUE(LEFT(L5,FIND("/",L5)-1))),IF(ISNUMBER(L5),L5,""))</f>
         <v/>
       </c>
       <c r="N5">
-        <f>IF(M5="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M5,'Summary '!$D$21:$D$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M5="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M5,'Summary '!$E$21:$E$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4730,12 +5086,12 @@
           <t>28/08/2026 - 12:30 to 17:00</t>
         </is>
       </c>
-      <c r="M6" s="51">
+      <c r="M6" s="59">
         <f>IFERROR(DATE(VALUE(MID(L6,FIND("/",L6,FIND("/",L6)+1)+1,4)),VALUE(MID(L6,FIND("/",L6)+1,FIND("/",L6,FIND("/",L6)+1)-FIND("/",L6)-1)),VALUE(LEFT(L6,FIND("/",L6)-1))),IF(ISNUMBER(L6),L6,""))</f>
         <v/>
       </c>
       <c r="N6">
-        <f>IF(M6="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M6,'Summary '!$D$21:$D$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M6="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M6,'Summary '!$E$21:$E$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4787,12 +5143,12 @@
           <t>31/08/2026 - 08:30 to 12:00</t>
         </is>
       </c>
-      <c r="M7" s="51">
+      <c r="M7" s="59">
         <f>IFERROR(DATE(VALUE(MID(L7,FIND("/",L7,FIND("/",L7)+1)+1,4)),VALUE(MID(L7,FIND("/",L7)+1,FIND("/",L7,FIND("/",L7)+1)-FIND("/",L7)-1)),VALUE(LEFT(L7,FIND("/",L7)-1))),IF(ISNUMBER(L7),L7,""))</f>
         <v/>
       </c>
       <c r="N7">
-        <f>IF(M7="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M7,'Summary '!$D$21:$D$36,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M7="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M7,'Summary '!$E$21:$E$36,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4844,12 +5200,12 @@
           <t>31/08/2026 - 12:30 to 17:00</t>
         </is>
       </c>
-      <c r="M8" s="51">
+      <c r="M8" s="59">
         <f>IFERROR(DATE(VALUE(MID(L8,FIND("/",L8,FIND("/",L8)+1)+1,4)),VALUE(MID(L8,FIND("/",L8)+1,FIND("/",L8,FIND("/",L8)+1)-FIND("/",L8)-1)),VALUE(LEFT(L8,FIND("/",L8)-1))),IF(ISNUMBER(L8),L8,""))</f>
         <v/>
       </c>
       <c r="N8">
-        <f>IF(M8="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M8,'Summary '!$D$21:$D$36,K8)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M8="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M8,'Summary '!$E$21:$E$36,K8)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4901,12 +5257,12 @@
           <t>1/09/2026 - 09:00 to 12:00</t>
         </is>
       </c>
-      <c r="M9" s="51">
+      <c r="M9" s="59">
         <f>IFERROR(DATE(VALUE(MID(L9,FIND("/",L9,FIND("/",L9)+1)+1,4)),VALUE(MID(L9,FIND("/",L9)+1,FIND("/",L9,FIND("/",L9)+1)-FIND("/",L9)-1)),VALUE(LEFT(L9,FIND("/",L9)-1))),IF(ISNUMBER(L9),L9,""))</f>
         <v/>
       </c>
       <c r="N9">
-        <f>IF(M9="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M9,'Summary '!$D$21:$D$36,K9)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M9="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M9,'Summary '!$E$21:$E$36,K9)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -4958,12 +5314,12 @@
           <t>1/09/2026 - 12:30 to 17:30</t>
         </is>
       </c>
-      <c r="M10" s="51">
+      <c r="M10" s="59">
         <f>IFERROR(DATE(VALUE(MID(L10,FIND("/",L10,FIND("/",L10)+1)+1,4)),VALUE(MID(L10,FIND("/",L10)+1,FIND("/",L10,FIND("/",L10)+1)-FIND("/",L10)-1)),VALUE(LEFT(L10,FIND("/",L10)-1))),IF(ISNUMBER(L10),L10,""))</f>
         <v/>
       </c>
       <c r="N10">
-        <f>IF(M10="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M10,'Summary '!$D$21:$D$36,K10)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M10="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M10,'Summary '!$E$21:$E$36,K10)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5015,12 +5371,12 @@
           <t>2/09/2026 - 09:00 to 12:00</t>
         </is>
       </c>
-      <c r="M11" s="51">
+      <c r="M11" s="59">
         <f>IFERROR(DATE(VALUE(MID(L11,FIND("/",L11,FIND("/",L11)+1)+1,4)),VALUE(MID(L11,FIND("/",L11)+1,FIND("/",L11,FIND("/",L11)+1)-FIND("/",L11)-1)),VALUE(LEFT(L11,FIND("/",L11)-1))),IF(ISNUMBER(L11),L11,""))</f>
         <v/>
       </c>
       <c r="N11">
-        <f>IF(M11="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M11,'Summary '!$D$21:$D$36,K11)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M11="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M11,'Summary '!$E$21:$E$36,K11)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5072,12 +5428,12 @@
           <t>2/09/2026 - 12:30 to 17:30</t>
         </is>
       </c>
-      <c r="M12" s="51">
+      <c r="M12" s="59">
         <f>IFERROR(DATE(VALUE(MID(L12,FIND("/",L12,FIND("/",L12)+1)+1,4)),VALUE(MID(L12,FIND("/",L12)+1,FIND("/",L12,FIND("/",L12)+1)-FIND("/",L12)-1)),VALUE(LEFT(L12,FIND("/",L12)-1))),IF(ISNUMBER(L12),L12,""))</f>
         <v/>
       </c>
       <c r="N12">
-        <f>IF(M12="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M12,'Summary '!$D$21:$D$36,K12)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M12="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M12,'Summary '!$E$21:$E$36,K12)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5129,12 +5485,12 @@
           <t>4/09/2026 - 08:30 to 12:00</t>
         </is>
       </c>
-      <c r="M13" s="51">
+      <c r="M13" s="59">
         <f>IFERROR(DATE(VALUE(MID(L13,FIND("/",L13,FIND("/",L13)+1)+1,4)),VALUE(MID(L13,FIND("/",L13)+1,FIND("/",L13,FIND("/",L13)+1)-FIND("/",L13)-1)),VALUE(LEFT(L13,FIND("/",L13)-1))),IF(ISNUMBER(L13),L13,""))</f>
         <v/>
       </c>
       <c r="N13">
-        <f>IF(M13="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M13,'Summary '!$D$21:$D$36,K13)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M13="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M13,'Summary '!$E$21:$E$36,K13)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5186,12 +5542,12 @@
           <t>4/09/2026 - 12:30 to 17:00</t>
         </is>
       </c>
-      <c r="M14" s="51">
+      <c r="M14" s="59">
         <f>IFERROR(DATE(VALUE(MID(L14,FIND("/",L14,FIND("/",L14)+1)+1,4)),VALUE(MID(L14,FIND("/",L14)+1,FIND("/",L14,FIND("/",L14)+1)-FIND("/",L14)-1)),VALUE(LEFT(L14,FIND("/",L14)-1))),IF(ISNUMBER(L14),L14,""))</f>
         <v/>
       </c>
       <c r="N14">
-        <f>IF(M14="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M14,'Summary '!$D$21:$D$36,K14)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M14="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M14,'Summary '!$E$21:$E$36,K14)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5299,12 +5655,12 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="M2" s="50" t="inlineStr">
+      <c r="M2" s="58" t="inlineStr">
         <is>
           <t>Work Date (helper)</t>
         </is>
       </c>
-      <c r="N2" s="50" t="inlineStr">
+      <c r="N2" s="58" t="inlineStr">
         <is>
           <t>Matched to Timesheet?</t>
         </is>
@@ -5358,12 +5714,12 @@
           <t>Reversal of incorrect rate for fortnight ending 07/08/2026</t>
         </is>
       </c>
-      <c r="M3" s="51">
+      <c r="M3" s="59">
         <f>IFERROR(DATE(VALUE(MID(L3,FIND("/",L3,FIND("/",L3)+1)+1,4)),VALUE(MID(L3,FIND("/",L3)+1,FIND("/",L3,FIND("/",L3)+1)-FIND("/",L3)-1)),VALUE(LEFT(L3,FIND("/",L3)-1))),IF(ISNUMBER(L3),L3,""))</f>
         <v/>
       </c>
       <c r="N3">
-        <f>IF(M3="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M3,'Summary '!$D$21:$D$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M3="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M3,'Summary '!$E$21:$E$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5415,12 +5771,12 @@
           <t>Reversal of incorrect rate for fortnight ending 07/08/2026</t>
         </is>
       </c>
-      <c r="M4" s="51">
+      <c r="M4" s="59">
         <f>IFERROR(DATE(VALUE(MID(L4,FIND("/",L4,FIND("/",L4)+1)+1,4)),VALUE(MID(L4,FIND("/",L4)+1,FIND("/",L4,FIND("/",L4)+1)-FIND("/",L4)-1)),VALUE(LEFT(L4,FIND("/",L4)-1))),IF(ISNUMBER(L4),L4,""))</f>
         <v/>
       </c>
       <c r="N4">
-        <f>IF(M4="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M4,'Summary '!$D$21:$D$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M4="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M4,'Summary '!$E$21:$E$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5472,12 +5828,12 @@
           <t xml:space="preserve">18/08/2026 - 07:00 to 12:00. 435 Bourke St - CBA </t>
         </is>
       </c>
-      <c r="M5" s="51">
+      <c r="M5" s="59">
         <f>IFERROR(DATE(VALUE(MID(L5,FIND("/",L5,FIND("/",L5)+1)+1,4)),VALUE(MID(L5,FIND("/",L5)+1,FIND("/",L5,FIND("/",L5)+1)-FIND("/",L5)-1)),VALUE(LEFT(L5,FIND("/",L5)-1))),IF(ISNUMBER(L5),L5,""))</f>
         <v/>
       </c>
       <c r="N5">
-        <f>IF(M5="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M5,'Summary '!$D$21:$D$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M5="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M5,'Summary '!$E$21:$E$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5529,12 +5885,12 @@
           <t xml:space="preserve">18/08/2026 - 13:00 to 16:00. 435 Bourke St - CBA </t>
         </is>
       </c>
-      <c r="M6" s="51">
+      <c r="M6" s="59">
         <f>IFERROR(DATE(VALUE(MID(L6,FIND("/",L6,FIND("/",L6)+1)+1,4)),VALUE(MID(L6,FIND("/",L6)+1,FIND("/",L6,FIND("/",L6)+1)-FIND("/",L6)-1)),VALUE(LEFT(L6,FIND("/",L6)-1))),IF(ISNUMBER(L6),L6,""))</f>
         <v/>
       </c>
       <c r="N6">
-        <f>IF(M6="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M6,'Summary '!$D$21:$D$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M6="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M6,'Summary '!$E$21:$E$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5586,12 +5942,12 @@
           <t>20/08/2026 - 13:00 to 17:00</t>
         </is>
       </c>
-      <c r="M7" s="51">
+      <c r="M7" s="59">
         <f>IFERROR(DATE(VALUE(MID(L7,FIND("/",L7,FIND("/",L7)+1)+1,4)),VALUE(MID(L7,FIND("/",L7)+1,FIND("/",L7,FIND("/",L7)+1)-FIND("/",L7)-1)),VALUE(LEFT(L7,FIND("/",L7)-1))),IF(ISNUMBER(L7),L7,""))</f>
         <v/>
       </c>
       <c r="N7">
-        <f>IF(M7="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M7,'Summary '!$D$21:$D$36,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M7="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M7,'Summary '!$E$21:$E$36,K7)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5698,12 +6054,12 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="M2" s="50" t="inlineStr">
+      <c r="M2" s="58" t="inlineStr">
         <is>
           <t>Work Date (helper)</t>
         </is>
       </c>
-      <c r="N2" s="50" t="inlineStr">
+      <c r="N2" s="58" t="inlineStr">
         <is>
           <t>Matched to Timesheet?</t>
         </is>
@@ -5755,12 +6111,12 @@
       <c r="L3" s="16" t="n">
         <v>46232</v>
       </c>
-      <c r="M3" s="51">
+      <c r="M3" s="59">
         <f>IFERROR(DATE(VALUE(MID(L3,FIND("/",L3,FIND("/",L3)+1)+1,4)),VALUE(MID(L3,FIND("/",L3)+1,FIND("/",L3,FIND("/",L3)+1)-FIND("/",L3)-1)),VALUE(LEFT(L3,FIND("/",L3)-1))),IF(ISNUMBER(L3),L3,""))</f>
         <v/>
       </c>
       <c r="N3">
-        <f>IF(M3="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M3,'Summary '!$D$21:$D$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M3="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M3,'Summary '!$E$21:$E$36,K3)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5810,12 +6166,12 @@
       <c r="L4" s="16" t="n">
         <v>46232</v>
       </c>
-      <c r="M4" s="51">
+      <c r="M4" s="59">
         <f>IFERROR(DATE(VALUE(MID(L4,FIND("/",L4,FIND("/",L4)+1)+1,4)),VALUE(MID(L4,FIND("/",L4)+1,FIND("/",L4,FIND("/",L4)+1)-FIND("/",L4)-1)),VALUE(LEFT(L4,FIND("/",L4)-1))),IF(ISNUMBER(L4),L4,""))</f>
         <v/>
       </c>
       <c r="N4">
-        <f>IF(M4="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M4,'Summary '!$D$21:$D$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M4="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M4,'Summary '!$E$21:$E$36,K4)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5865,12 +6221,12 @@
       <c r="L5" s="16" t="n">
         <v>46233</v>
       </c>
-      <c r="M5" s="51">
+      <c r="M5" s="59">
         <f>IFERROR(DATE(VALUE(MID(L5,FIND("/",L5,FIND("/",L5)+1)+1,4)),VALUE(MID(L5,FIND("/",L5)+1,FIND("/",L5,FIND("/",L5)+1)-FIND("/",L5)-1)),VALUE(LEFT(L5,FIND("/",L5)-1))),IF(ISNUMBER(L5),L5,""))</f>
         <v/>
       </c>
       <c r="N5">
-        <f>IF(M5="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M5,'Summary '!$D$21:$D$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M5="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M5,'Summary '!$E$21:$E$36,K5)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
@@ -5920,12 +6276,12 @@
       <c r="L6" s="16" t="n">
         <v>46233</v>
       </c>
-      <c r="M6" s="51">
+      <c r="M6" s="59">
         <f>IFERROR(DATE(VALUE(MID(L6,FIND("/",L6,FIND("/",L6)+1)+1,4)),VALUE(MID(L6,FIND("/",L6)+1,FIND("/",L6,FIND("/",L6)+1)-FIND("/",L6)-1)),VALUE(LEFT(L6,FIND("/",L6)-1))),IF(ISNUMBER(L6),L6,""))</f>
         <v/>
       </c>
       <c r="N6">
-        <f>IF(M6="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M6,'Summary '!$D$21:$D$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
+        <f>IF(M6="","No - adjustment line (no work date)",IF(COUNTIFS('Summary '!$A$21:$A$36,M6,'Summary '!$E$21:$E$36,K6)&gt;0,"Yes","NO MATCH - INVESTIGATE"))</f>
         <v/>
       </c>
     </row>
